--- a/Data/Default Encounters By Zone.xlsx
+++ b/Data/Default Encounters By Zone.xlsx
@@ -1,885 +1,978 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Brian McDaniel\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Store\Code\TCControlPanel\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47E58186-3026-41BF-8BF1-8B59A985053C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1703BAE-A0DD-4EFF-B491-372BAEE998F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2955" yWindow="2205" windowWidth="23745" windowHeight="11850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13875" yWindow="2363" windowWidth="13958" windowHeight="12382" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Encounters by Zone" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="380">
+  <si>
+    <t>Meadows</t>
+  </si>
+  <si>
+    <t>Farmland</t>
+  </si>
+  <si>
+    <t>Rolling Hills</t>
+  </si>
+  <si>
+    <t>Craggy Hills</t>
+  </si>
+  <si>
+    <t>Mountains</t>
+  </si>
+  <si>
+    <t>Light Forest</t>
+  </si>
+  <si>
+    <t>Dense Forest</t>
+  </si>
+  <si>
+    <t>Thorny Forest</t>
+  </si>
+  <si>
+    <t>Fungal Forest</t>
+  </si>
+  <si>
+    <t>Bogs</t>
+  </si>
+  <si>
+    <t>Swamps</t>
+  </si>
+  <si>
+    <t>Lakes</t>
+  </si>
+  <si>
+    <t>Seas</t>
+  </si>
+  <si>
+    <t>Roads</t>
+  </si>
+  <si>
+    <t>Rivers</t>
+  </si>
+  <si>
+    <t>Settlements</t>
+  </si>
+  <si>
+    <t>Ruins</t>
+  </si>
+  <si>
+    <t>Caverns</t>
+  </si>
+  <si>
+    <t>Dungeons</t>
+  </si>
   <si>
     <t>Encounter</t>
   </si>
   <si>
-    <t>Meadows</t>
-  </si>
-  <si>
-    <t>Farmland</t>
-  </si>
-  <si>
-    <t>Rolling Hills</t>
-  </si>
-  <si>
-    <t>Craggy Hills</t>
-  </si>
-  <si>
-    <t>Mountains</t>
-  </si>
-  <si>
-    <t>Light Forest</t>
-  </si>
-  <si>
-    <t>Dense Forest</t>
-  </si>
-  <si>
-    <t>Thorny Forest</t>
-  </si>
-  <si>
-    <t>Fungal Forest</t>
-  </si>
-  <si>
-    <t>Bogs</t>
-  </si>
-  <si>
-    <t>Swamps</t>
-  </si>
-  <si>
-    <t>Lakes</t>
-  </si>
-  <si>
-    <t>Seas</t>
-  </si>
-  <si>
-    <t>Roads</t>
-  </si>
-  <si>
-    <t>Rivers</t>
-  </si>
-  <si>
-    <t>Settlements</t>
-  </si>
-  <si>
-    <t>Ruins</t>
-  </si>
-  <si>
-    <t>Caverns</t>
-  </si>
-  <si>
-    <t>Dungeons</t>
+    <t>Aurochs</t>
+  </si>
+  <si>
+    <t>Badger, Argentvorax</t>
+  </si>
+  <si>
+    <t>Badger, Aurumvorax</t>
+  </si>
+  <si>
+    <t>Badger, Giant</t>
+  </si>
+  <si>
+    <t>Bandersnatch</t>
+  </si>
+  <si>
+    <t>Basilisk</t>
+  </si>
+  <si>
+    <t>Bat, Giant</t>
+  </si>
+  <si>
+    <t>Bat, Hunter</t>
+  </si>
+  <si>
+    <t>Bat, Needle-Nosed</t>
+  </si>
+  <si>
+    <t>Bear, Brown</t>
+  </si>
+  <si>
+    <t>Bear, Cave</t>
+  </si>
+  <si>
+    <t>Boar</t>
+  </si>
+  <si>
+    <t>Boar, Razorback</t>
+  </si>
+  <si>
+    <t>Carp, King</t>
+  </si>
+  <si>
+    <t>Catamount</t>
+  </si>
+  <si>
+    <t>Catoblepas</t>
+  </si>
+  <si>
+    <t>Chimera</t>
+  </si>
+  <si>
+    <t>Cockatrice</t>
+  </si>
+  <si>
+    <t>Crocodile</t>
+  </si>
+  <si>
+    <t>Deer, False Unicorn</t>
+  </si>
+  <si>
+    <t>Deer, Red</t>
+  </si>
+  <si>
+    <t>Devil-Goat</t>
+  </si>
+  <si>
+    <t>Displacer Cat</t>
+  </si>
+  <si>
+    <t>Elk</t>
+  </si>
+  <si>
+    <t>Froghemoth</t>
+  </si>
+  <si>
+    <t>Galosher</t>
+  </si>
+  <si>
+    <t>Goat, Ibex</t>
+  </si>
+  <si>
+    <t>Grell</t>
+  </si>
+  <si>
+    <t>Griffon</t>
+  </si>
+  <si>
+    <t>Harpy</t>
+  </si>
+  <si>
+    <t>Heron, Giant</t>
+  </si>
+  <si>
+    <t>Hippocampus</t>
+  </si>
+  <si>
+    <t>Hippogriff</t>
+  </si>
+  <si>
+    <t>Hodag</t>
+  </si>
+  <si>
+    <t>Hook Horror</t>
+  </si>
+  <si>
+    <t>Horse, Flying</t>
+  </si>
+  <si>
+    <t>Horse, Wild</t>
+  </si>
+  <si>
+    <t>Iron Bull</t>
+  </si>
+  <si>
+    <t>Jabberwock</t>
+  </si>
+  <si>
+    <t>Land Shark</t>
+  </si>
+  <si>
+    <t>Leucrotta</t>
+  </si>
+  <si>
+    <t>Lynx</t>
+  </si>
+  <si>
+    <t>Mammoth</t>
+  </si>
+  <si>
+    <t>Mammoth, Miniature</t>
+  </si>
+  <si>
+    <t>Manticore</t>
+  </si>
+  <si>
+    <t>Medusa</t>
+  </si>
+  <si>
+    <t>Monkey, Flying</t>
+  </si>
+  <si>
+    <t>Owlbear</t>
+  </si>
+  <si>
+    <t>Peryton</t>
+  </si>
+  <si>
+    <t>Pike, Giant</t>
+  </si>
+  <si>
+    <t>Po-Wit Bird</t>
+  </si>
+  <si>
+    <t>Porcupine, Giant</t>
+  </si>
+  <si>
+    <t>Possum, Giant</t>
+  </si>
+  <si>
+    <t>Purple Worm</t>
+  </si>
+  <si>
+    <t>Rat, Giant</t>
+  </si>
+  <si>
+    <t>Roc</t>
+  </si>
+  <si>
+    <t>Sabre-Tooth Lion</t>
+  </si>
+  <si>
+    <t>Salmon, Spike-Tooth</t>
+  </si>
+  <si>
+    <t>Skunk, Giant</t>
+  </si>
+  <si>
+    <t>Snake, Adder</t>
+  </si>
+  <si>
+    <t>Snake, Asp</t>
+  </si>
+  <si>
+    <t>Snake, Copperhead</t>
+  </si>
+  <si>
+    <t>Snake, Cottonmouth</t>
+  </si>
+  <si>
+    <t>Snake, Giant Copperhead</t>
+  </si>
+  <si>
+    <t>Snake, Giant Cottonmouth</t>
+  </si>
+  <si>
+    <t>Snake, Giant Timber Rattler</t>
+  </si>
+  <si>
+    <t>Snake, Giant Viper</t>
+  </si>
+  <si>
+    <t>Snake, Hoopsnake</t>
+  </si>
+  <si>
+    <t>Snake, Hypnoviper</t>
+  </si>
+  <si>
+    <t>Snake, Timber Rattler</t>
+  </si>
+  <si>
+    <t>Snake, Viper</t>
+  </si>
+  <si>
+    <t>Sturgeon, Giant</t>
+  </si>
+  <si>
+    <t>Tunny Fish, Flying</t>
+  </si>
+  <si>
+    <t>Turtle, Giant Snapping</t>
+  </si>
+  <si>
+    <t>Turtle, River</t>
+  </si>
+  <si>
+    <t>Walrus</t>
+  </si>
+  <si>
+    <t>Weasel, Giant</t>
+  </si>
+  <si>
+    <t>Whale, Oil</t>
+  </si>
+  <si>
+    <t>Whale, Tusked</t>
+  </si>
+  <si>
+    <t>Wolf</t>
+  </si>
+  <si>
+    <t>Ankheg</t>
+  </si>
+  <si>
+    <t>Bat Swarm</t>
+  </si>
+  <si>
+    <t>Bee Swarm</t>
+  </si>
+  <si>
+    <t>Beetle, Giant Fire</t>
+  </si>
+  <si>
+    <t>Beetle, Giant Horned</t>
+  </si>
+  <si>
+    <t>Beetle, Giant Lightning</t>
+  </si>
+  <si>
+    <t>Beetle, Giant Oil</t>
+  </si>
+  <si>
+    <t>Carcass Crawler</t>
+  </si>
+  <si>
+    <t>Cave Fisher</t>
+  </si>
+  <si>
+    <t>Centipede, Golden</t>
+  </si>
+  <si>
+    <t>Centipede, Night-Runner</t>
+  </si>
+  <si>
+    <t>Centipede, Red-Leg</t>
+  </si>
+  <si>
+    <t>Crab, Bone</t>
+  </si>
+  <si>
+    <t>Crab, Fierce</t>
+  </si>
+  <si>
+    <t>Crab, Giant Stone</t>
+  </si>
+  <si>
+    <t>Crab, Hulking</t>
+  </si>
+  <si>
+    <t>Crayfish, Giant Golden</t>
+  </si>
+  <si>
+    <t>Crayfish, Hulking</t>
+  </si>
+  <si>
+    <t>Dragonfly, Giant</t>
+  </si>
+  <si>
+    <t>Firefly, Giant</t>
+  </si>
+  <si>
+    <t>Fly, Giant Bluebottle</t>
+  </si>
+  <si>
+    <t>Fly, Giant Gadfly</t>
+  </si>
+  <si>
+    <t>Fly, Giant Robberfly</t>
+  </si>
+  <si>
+    <t>Frog, Maneating</t>
+  </si>
+  <si>
+    <t>Leech Swarm</t>
+  </si>
+  <si>
+    <t>Leech, Giant</t>
+  </si>
+  <si>
+    <t>Locust, Giant Cave</t>
+  </si>
+  <si>
+    <t>Moth, Giant Eye</t>
+  </si>
+  <si>
+    <t>Newt, Bog</t>
+  </si>
+  <si>
+    <t>Newt, Cave</t>
+  </si>
+  <si>
+    <t>Newt, Red</t>
+  </si>
+  <si>
+    <t>Newt, Spotted</t>
+  </si>
+  <si>
+    <t>Rat Swarm</t>
+  </si>
+  <si>
+    <t>Rust Bug</t>
+  </si>
+  <si>
+    <t>Scorpion, Giant Cave</t>
+  </si>
+  <si>
+    <t>Scorpion, Giant Morscauda</t>
+  </si>
+  <si>
+    <t>Scorpion, Giant Tenebrarius</t>
+  </si>
+  <si>
+    <t>Slug, Giant Spitting</t>
+  </si>
+  <si>
+    <t>Snail, Giant</t>
+  </si>
+  <si>
+    <t>Spider Swarm</t>
+  </si>
+  <si>
+    <t>Spider, Cave</t>
+  </si>
+  <si>
+    <t>Spider, Dark Widow</t>
+  </si>
+  <si>
+    <t>Spider, Hunter</t>
+  </si>
+  <si>
+    <t>Spider, Luteback</t>
+  </si>
+  <si>
+    <t>Spider, Tarantella</t>
+  </si>
+  <si>
+    <t>Spider, Tube</t>
+  </si>
+  <si>
+    <t>Spider, Yellow-Banded Orbweaver</t>
+  </si>
+  <si>
+    <t>Wasp, Giant Paper</t>
+  </si>
+  <si>
+    <t>Water Termite, Giant</t>
+  </si>
+  <si>
+    <t>Goblin, Lurker</t>
+  </si>
+  <si>
+    <t>Goblin, Merchant</t>
+  </si>
+  <si>
+    <t>Goblin, Scrub</t>
+  </si>
+  <si>
+    <t>Ogre</t>
+  </si>
+  <si>
+    <t>Orc</t>
+  </si>
+  <si>
+    <t>Orc, Cave</t>
+  </si>
+  <si>
+    <t>Redcap</t>
+  </si>
+  <si>
+    <t>Unicorn</t>
+  </si>
+  <si>
+    <t>Wyrm, Black Bile</t>
+  </si>
+  <si>
+    <t>Wyrm, Blood</t>
+  </si>
+  <si>
+    <t>Wyrm, Maegen</t>
+  </si>
+  <si>
+    <t>Wyrm, Phlegm</t>
+  </si>
+  <si>
+    <t>Wyrm, Tatzelwyrm</t>
+  </si>
+  <si>
+    <t>Wyrm, Yellow Bile</t>
+  </si>
+  <si>
+    <t>Wyvern</t>
+  </si>
+  <si>
+    <t>Barrowbogey</t>
+  </si>
+  <si>
+    <t>Boggin</t>
+  </si>
+  <si>
+    <t>Elf, Courtier</t>
+  </si>
+  <si>
+    <t>Elf, Knight</t>
+  </si>
+  <si>
+    <t>Elf, Maiden</t>
+  </si>
+  <si>
+    <t>Elf, Wanderer</t>
+  </si>
+  <si>
+    <t>Huldra</t>
+  </si>
+  <si>
+    <t>Kelpie</t>
+  </si>
+  <si>
+    <t>Merfaun</t>
+  </si>
+  <si>
+    <t>Merman</t>
+  </si>
+  <si>
+    <t>Murmurin</t>
+  </si>
+  <si>
+    <t>Nack</t>
+  </si>
+  <si>
+    <t>Nutcap</t>
+  </si>
+  <si>
+    <t>Selkie</t>
+  </si>
+  <si>
+    <t>Sprite</t>
+  </si>
+  <si>
+    <t>Swanmay</t>
+  </si>
+  <si>
+    <t>The Hag</t>
+  </si>
+  <si>
+    <t>Troll</t>
+  </si>
+  <si>
+    <t>Troll, Moss</t>
+  </si>
+  <si>
+    <t>Troll, Mountain</t>
+  </si>
+  <si>
+    <t>Vulpine</t>
+  </si>
+  <si>
+    <t>Wild Hunt</t>
+  </si>
+  <si>
+    <t>Yickerwill</t>
+  </si>
+  <si>
+    <t>Brown Mold</t>
+  </si>
+  <si>
+    <t>Gas Spore</t>
+  </si>
+  <si>
+    <t>Green Slime</t>
+  </si>
+  <si>
+    <t>Mushroom Men</t>
+  </si>
+  <si>
+    <t>Shrieker</t>
+  </si>
+  <si>
+    <t>Violet Mushroom</t>
+  </si>
+  <si>
+    <t>Whitecap Mushroom</t>
+  </si>
+  <si>
+    <t>Yellow Mold</t>
+  </si>
+  <si>
+    <t>Breggle, Crookhorn</t>
+  </si>
+  <si>
+    <t>Breggle, Longhorn</t>
+  </si>
+  <si>
+    <t>Breggle, Shorthorn</t>
+  </si>
+  <si>
+    <t>Centaur</t>
+  </si>
+  <si>
+    <t>Cobbin</t>
+  </si>
+  <si>
+    <t>Deorling</t>
+  </si>
+  <si>
+    <t>Dwarf, Artisan</t>
+  </si>
+  <si>
+    <t>Dwarf, Mercenary</t>
+  </si>
+  <si>
+    <t>Dwarf, Moneylender</t>
+  </si>
+  <si>
+    <t>Dwarf, Stonemason</t>
+  </si>
+  <si>
+    <t>Dwarf, Tinker</t>
+  </si>
+  <si>
+    <t>Dwarf, Traveling Smith</t>
+  </si>
+  <si>
+    <t>Giant</t>
+  </si>
+  <si>
+    <t>Giant, Ettin</t>
+  </si>
+  <si>
+    <t>Giant, Fomorian</t>
+  </si>
+  <si>
+    <t>Giant, True</t>
+  </si>
+  <si>
+    <t>Halfling, Artisan</t>
+  </si>
+  <si>
+    <t>Halfling, Scout</t>
+  </si>
+  <si>
+    <t>Halfling, Wanderer</t>
+  </si>
+  <si>
+    <t>Harridan</t>
+  </si>
+  <si>
+    <t>Men, Adventuring Party</t>
+  </si>
+  <si>
+    <t>Men, Bandit</t>
+  </si>
+  <si>
+    <t>Men, Beggar</t>
+  </si>
+  <si>
+    <t>Men, Churchman</t>
+  </si>
+  <si>
+    <t>Men, Cultists</t>
+  </si>
+  <si>
+    <t>Men, Drune Audrune</t>
+  </si>
+  <si>
+    <t>Men, Drune Braithmaid</t>
+  </si>
+  <si>
+    <t>Men, Drune Cottager</t>
+  </si>
+  <si>
+    <t>Men, Drune Drunewife</t>
+  </si>
+  <si>
+    <t>Men, Drune Wandering</t>
+  </si>
+  <si>
+    <t>Men, Fighter</t>
+  </si>
+  <si>
+    <t>Men, Fisher</t>
+  </si>
+  <si>
+    <t>Men, Herbalist</t>
+  </si>
+  <si>
+    <t>Men, Herder</t>
+  </si>
+  <si>
+    <t>Men, Hermit</t>
+  </si>
+  <si>
+    <t>Men, Hunter</t>
+  </si>
+  <si>
+    <t>Men, Knight</t>
+  </si>
+  <si>
+    <t>Men, Lost Soul</t>
+  </si>
+  <si>
+    <t>Men, Mercenary</t>
+  </si>
+  <si>
+    <t>Men, Merchant</t>
+  </si>
+  <si>
+    <t>Men, Messenger</t>
+  </si>
+  <si>
+    <t>Men, Noble</t>
+  </si>
+  <si>
+    <t>Men, Patrol</t>
+  </si>
+  <si>
+    <t>Men, Trapper</t>
+  </si>
+  <si>
+    <t>Men, Truffle Hunter</t>
+  </si>
+  <si>
+    <t>Men, Villager</t>
+  </si>
+  <si>
+    <t>Men, Witch</t>
+  </si>
+  <si>
+    <t>Men, Wizard</t>
+  </si>
+  <si>
+    <t>Men, Woodcutter</t>
+  </si>
+  <si>
+    <t>Minotaur</t>
+  </si>
+  <si>
+    <t>Mossling, Bargeman</t>
+  </si>
+  <si>
+    <t>Mossling, Mold Oracle</t>
+  </si>
+  <si>
+    <t>Mossling, Moss Gatherer</t>
+  </si>
+  <si>
+    <t>Wodewose</t>
+  </si>
+  <si>
+    <t>Wolf, Corrupted</t>
+  </si>
+  <si>
+    <t>Wolperdingle</t>
+  </si>
+  <si>
+    <t>Wrong'un</t>
+  </si>
+  <si>
+    <t>Basic Ooze</t>
+  </si>
+  <si>
+    <t>Black Ooze</t>
+  </si>
+  <si>
+    <t>Blood Ooze</t>
+  </si>
+  <si>
+    <t>Crystal Ooze</t>
+  </si>
+  <si>
+    <t>Gelatinous Cube</t>
+  </si>
+  <si>
+    <t>Mimic</t>
+  </si>
+  <si>
+    <t>Ochre Ooze</t>
+  </si>
+  <si>
+    <t>Otyugh</t>
+  </si>
+  <si>
+    <t>Atacorn</t>
+  </si>
+  <si>
+    <t>Atanuwë</t>
+  </si>
+  <si>
+    <t>Black Tentacles</t>
+  </si>
+  <si>
+    <t>Familiar Demon</t>
+  </si>
+  <si>
+    <t>Shadow Demon</t>
+  </si>
+  <si>
+    <t>Succubus Demon</t>
+  </si>
+  <si>
+    <t>Wendigo Demon</t>
+  </si>
+  <si>
+    <t>Werebear Demon</t>
+  </si>
+  <si>
+    <t>Werewolf Demon</t>
+  </si>
+  <si>
+    <t>Big Chook</t>
+  </si>
+  <si>
+    <t>Effigy Armor</t>
+  </si>
+  <si>
+    <t>Effigy Statue</t>
+  </si>
+  <si>
+    <t>Everburning Salamander</t>
+  </si>
+  <si>
+    <t>Gargoyle</t>
+  </si>
+  <si>
+    <t>Living Door</t>
+  </si>
+  <si>
+    <t>Root Thing</t>
+  </si>
+  <si>
+    <t>Roper/Piercer</t>
+  </si>
+  <si>
+    <t>Rug of Smothering</t>
+  </si>
+  <si>
+    <t>Scarecrow</t>
+  </si>
+  <si>
+    <t>Ship's Figurehead</t>
+  </si>
+  <si>
+    <t>Treowere</t>
+  </si>
+  <si>
+    <t>Treowere, Corrupted</t>
+  </si>
+  <si>
+    <t>Tunnel Hulk</t>
+  </si>
+  <si>
+    <t>Wandering Tower</t>
+  </si>
+  <si>
+    <t>Water Weird</t>
+  </si>
+  <si>
+    <t>Weathervane Effigy</t>
   </si>
   <si>
     <t>Air Elemental</t>
   </si>
   <si>
-    <t>Ankheg</t>
-  </si>
-  <si>
-    <t>Atacorn</t>
-  </si>
-  <si>
-    <t>Atanuwë</t>
-  </si>
-  <si>
-    <t>Aurochs</t>
-  </si>
-  <si>
-    <t>Badger, Argentvorax</t>
-  </si>
-  <si>
-    <t>Badger, Aurumvorax</t>
-  </si>
-  <si>
-    <t>Badger, Giant</t>
-  </si>
-  <si>
-    <t>Bandersnatch</t>
+    <t>Earth Elemental</t>
+  </si>
+  <si>
+    <t>Fire Elemental</t>
+  </si>
+  <si>
+    <t>Ice Elemental</t>
+  </si>
+  <si>
+    <t>Water Elemental</t>
+  </si>
+  <si>
+    <t>Ghost, Antler-Wraith</t>
+  </si>
+  <si>
+    <t>Ghost, Banshee</t>
+  </si>
+  <si>
+    <t>Ghost, Dullahan</t>
+  </si>
+  <si>
+    <t>Ghost, Generic</t>
+  </si>
+  <si>
+    <t>Ghost, Will-o-Wisp</t>
+  </si>
+  <si>
+    <t>Ghost, Wraith</t>
+  </si>
+  <si>
+    <t>Ghost, Yeth Hound</t>
+  </si>
+  <si>
+    <t>Bramble Golem</t>
+  </si>
+  <si>
+    <t>Bronze Golem</t>
+  </si>
+  <si>
+    <t>Clay Golem</t>
+  </si>
+  <si>
+    <t>Gingerbread Golem</t>
+  </si>
+  <si>
+    <t>Glass Golem</t>
+  </si>
+  <si>
+    <t>Homunculus Golem</t>
+  </si>
+  <si>
+    <t>Iron Golem</t>
+  </si>
+  <si>
+    <t>Kiln-Fired Golem</t>
+  </si>
+  <si>
+    <t>Pretzel Golem</t>
+  </si>
+  <si>
+    <t>Wax Golem</t>
+  </si>
+  <si>
+    <t>Wicker Golem</t>
   </si>
   <si>
     <t>Barrow-Wight</t>
   </si>
   <si>
-    <t>Barrowbogey</t>
-  </si>
-  <si>
-    <t>Basic Ooze</t>
-  </si>
-  <si>
-    <t>Basilisk</t>
-  </si>
-  <si>
-    <t>Bat Swarm</t>
-  </si>
-  <si>
-    <t>Bat, Giant</t>
-  </si>
-  <si>
-    <t>Bat, Hunter</t>
-  </si>
-  <si>
-    <t>Bat, Needle-Nosed</t>
-  </si>
-  <si>
-    <t>Bear, Brown</t>
-  </si>
-  <si>
-    <t>Bear, Cave</t>
-  </si>
-  <si>
-    <t>Bee Swarm</t>
-  </si>
-  <si>
-    <t>Beetle, Giant Fire</t>
-  </si>
-  <si>
-    <t>Beetle, Giant Horned</t>
-  </si>
-  <si>
-    <t>Beetle, Giant Lightning</t>
-  </si>
-  <si>
-    <t>Beetle, Giant Oil</t>
-  </si>
-  <si>
-    <t>Big Chook</t>
-  </si>
-  <si>
-    <t>Black Ooze</t>
-  </si>
-  <si>
-    <t>Black Tentacles</t>
-  </si>
-  <si>
-    <t>Blood Ooze</t>
-  </si>
-  <si>
-    <t>Boar</t>
-  </si>
-  <si>
-    <t>Boar, Razorback</t>
-  </si>
-  <si>
-    <t>Boggin</t>
-  </si>
-  <si>
-    <t>Bramble Golem</t>
-  </si>
-  <si>
-    <t>Breggle, Crookhorn</t>
-  </si>
-  <si>
-    <t>Breggle, Longhorn</t>
-  </si>
-  <si>
-    <t>Breggle, Shorthorn</t>
-  </si>
-  <si>
-    <t>Bronze Golem</t>
-  </si>
-  <si>
-    <t>Brown Mold</t>
-  </si>
-  <si>
-    <t>Carcass Crawler</t>
-  </si>
-  <si>
-    <t>Carp, King</t>
-  </si>
-  <si>
-    <t>Catamount</t>
-  </si>
-  <si>
-    <t>Catoblepas</t>
-  </si>
-  <si>
-    <t>Cave Fisher</t>
-  </si>
-  <si>
-    <t>Centaur</t>
-  </si>
-  <si>
-    <t>Centipede, Golden</t>
-  </si>
-  <si>
-    <t>Centipede, Night-Runner</t>
-  </si>
-  <si>
-    <t>Centipede, Red-Leg</t>
-  </si>
-  <si>
-    <t>Chimera</t>
-  </si>
-  <si>
-    <t>Clay Golem</t>
-  </si>
-  <si>
-    <t>Cobbin</t>
-  </si>
-  <si>
-    <t>Cockatrice</t>
-  </si>
-  <si>
-    <t>Crab, Bone</t>
-  </si>
-  <si>
-    <t>Crab, Fierce</t>
-  </si>
-  <si>
-    <t>Crab, Giant Stone</t>
-  </si>
-  <si>
-    <t>Crab, Hulking</t>
-  </si>
-  <si>
-    <t>Crayfish, Giant Golden</t>
-  </si>
-  <si>
-    <t>Crayfish, Hulking</t>
-  </si>
-  <si>
-    <t>Crocodile</t>
-  </si>
-  <si>
-    <t>Crystal Ooze</t>
-  </si>
-  <si>
-    <t>Deer, False Unicorn</t>
-  </si>
-  <si>
-    <t>Deer, Red</t>
-  </si>
-  <si>
-    <t>Deorling</t>
-  </si>
-  <si>
-    <t>Devil-Goat</t>
-  </si>
-  <si>
-    <t>Displacer Cat</t>
-  </si>
-  <si>
-    <t>Dragonfly, Giant</t>
-  </si>
-  <si>
-    <t>Dwarf, Artisan</t>
-  </si>
-  <si>
-    <t>Dwarf, Mercenary</t>
-  </si>
-  <si>
-    <t>Dwarf, Moneylender</t>
-  </si>
-  <si>
-    <t>Dwarf, Stonemason</t>
-  </si>
-  <si>
-    <t>Dwarf, Tinker</t>
-  </si>
-  <si>
-    <t>Dwarf, Traveling Smith</t>
-  </si>
-  <si>
-    <t>Earth Elemental</t>
-  </si>
-  <si>
-    <t>Effigy Armor</t>
-  </si>
-  <si>
-    <t>Effigy Statue</t>
-  </si>
-  <si>
-    <t>Elf, Courtier</t>
-  </si>
-  <si>
-    <t>Elf, Knight</t>
-  </si>
-  <si>
-    <t>Elf, Maiden</t>
-  </si>
-  <si>
-    <t>Elf, Wanderer</t>
-  </si>
-  <si>
-    <t>Elk</t>
-  </si>
-  <si>
-    <t>Everburning Salamander</t>
-  </si>
-  <si>
-    <t>Familiar Demon</t>
-  </si>
-  <si>
-    <t>Fire Elemental</t>
-  </si>
-  <si>
-    <t>Firefly, Giant</t>
-  </si>
-  <si>
-    <t>Fly, Giant Bluebottle</t>
-  </si>
-  <si>
-    <t>Fly, Giant Gadfly</t>
-  </si>
-  <si>
-    <t>Fly, Giant Robberfly</t>
-  </si>
-  <si>
-    <t>Frog, Maneating</t>
-  </si>
-  <si>
-    <t>Froghemoth</t>
-  </si>
-  <si>
     <t>Gallows-Wight</t>
   </si>
   <si>
-    <t>Galosher</t>
-  </si>
-  <si>
-    <t>Gargoyle</t>
-  </si>
-  <si>
-    <t>Gas Spore</t>
-  </si>
-  <si>
-    <t>Gelatinous Cube</t>
-  </si>
-  <si>
-    <t>Ghost, Antler-Wraith</t>
-  </si>
-  <si>
-    <t>Ghost, Banshee</t>
-  </si>
-  <si>
-    <t>Ghost, Dullahan</t>
-  </si>
-  <si>
-    <t>Ghost, Generic</t>
-  </si>
-  <si>
-    <t>Ghost, Will-o-Wisp</t>
-  </si>
-  <si>
-    <t>Ghost, Wraith</t>
-  </si>
-  <si>
-    <t>Ghost, Yeth Hound</t>
-  </si>
-  <si>
     <t>Ghoul</t>
   </si>
   <si>
-    <t>Giant</t>
-  </si>
-  <si>
-    <t>Giant, Ettin</t>
-  </si>
-  <si>
-    <t>Giant, Fomorian</t>
-  </si>
-  <si>
-    <t>Giant, True</t>
-  </si>
-  <si>
-    <t>Gingerbread Golem</t>
-  </si>
-  <si>
-    <t>Glass Golem</t>
-  </si>
-  <si>
     <t>Gloam</t>
   </si>
   <si>
-    <t>Goat, Ibex</t>
-  </si>
-  <si>
-    <t>Goblin, Lurker</t>
-  </si>
-  <si>
-    <t>Goblin, Merchant</t>
-  </si>
-  <si>
-    <t>Goblin, Scrub</t>
-  </si>
-  <si>
-    <t>Green Slime</t>
-  </si>
-  <si>
-    <t>Grell</t>
-  </si>
-  <si>
-    <t>Griffon</t>
-  </si>
-  <si>
-    <t>Halfling, Artisan</t>
-  </si>
-  <si>
-    <t>Halfling, Scout</t>
-  </si>
-  <si>
-    <t>Halfling, Wanderer</t>
-  </si>
-  <si>
-    <t>Harpy</t>
-  </si>
-  <si>
-    <t>Harridan</t>
-  </si>
-  <si>
-    <t>Heron, Giant</t>
-  </si>
-  <si>
-    <t>Hippocampus</t>
-  </si>
-  <si>
-    <t>Hippogriff</t>
-  </si>
-  <si>
-    <t>Hodag</t>
-  </si>
-  <si>
-    <t>Homunculus Golem</t>
-  </si>
-  <si>
-    <t>Hook Horror</t>
-  </si>
-  <si>
-    <t>Horse, Flying</t>
-  </si>
-  <si>
-    <t>Horse, Wild</t>
-  </si>
-  <si>
-    <t>Huldra</t>
-  </si>
-  <si>
-    <t>Ice Elemental</t>
-  </si>
-  <si>
-    <t>Iron Bull</t>
-  </si>
-  <si>
-    <t>Iron Golem</t>
-  </si>
-  <si>
-    <t>Jabberwock</t>
-  </si>
-  <si>
-    <t>Kelpie</t>
-  </si>
-  <si>
-    <t>Kiln-Fired Golem</t>
-  </si>
-  <si>
-    <t>Land Shark</t>
-  </si>
-  <si>
-    <t>Leech Swarm</t>
-  </si>
-  <si>
-    <t>Leech, Giant</t>
-  </si>
-  <si>
-    <t>Leucrotta</t>
-  </si>
-  <si>
-    <t>Living Door</t>
-  </si>
-  <si>
-    <t>Locust, Giant Cave</t>
-  </si>
-  <si>
-    <t>Lynx</t>
-  </si>
-  <si>
-    <t>Mammoth</t>
-  </si>
-  <si>
-    <t>Mammoth, Miniature</t>
-  </si>
-  <si>
-    <t>Manticore</t>
-  </si>
-  <si>
-    <t>Medusa</t>
-  </si>
-  <si>
-    <t>Men, Adventuring Party</t>
-  </si>
-  <si>
-    <t>Men, Bandit</t>
-  </si>
-  <si>
-    <t>Men, Beggar</t>
-  </si>
-  <si>
-    <t>Men, Churchman</t>
-  </si>
-  <si>
-    <t>Men, Cultists</t>
-  </si>
-  <si>
-    <t>Men, Drune Audrune</t>
-  </si>
-  <si>
-    <t>Men, Drune Braithmaid</t>
-  </si>
-  <si>
-    <t>Men, Drune Cottager</t>
-  </si>
-  <si>
-    <t>Men, Drune Drunewife</t>
-  </si>
-  <si>
-    <t>Men, Drune Wandering</t>
-  </si>
-  <si>
-    <t>Men, Fighter</t>
-  </si>
-  <si>
-    <t>Men, Fisher</t>
-  </si>
-  <si>
-    <t>Men, Herbalist</t>
-  </si>
-  <si>
-    <t>Men, Herder</t>
-  </si>
-  <si>
-    <t>Men, Hermit</t>
-  </si>
-  <si>
-    <t>Men, Hunter</t>
-  </si>
-  <si>
-    <t>Men, Knight</t>
-  </si>
-  <si>
-    <t>Men, Lost Soul</t>
-  </si>
-  <si>
-    <t>Men, Mercenary</t>
-  </si>
-  <si>
-    <t>Men, Merchant</t>
-  </si>
-  <si>
-    <t>Men, Messenger</t>
-  </si>
-  <si>
-    <t>Men, Noble</t>
-  </si>
-  <si>
-    <t>Men, Patrol</t>
-  </si>
-  <si>
-    <t>Men, Trapper</t>
-  </si>
-  <si>
-    <t>Men, Truffle Hunter</t>
-  </si>
-  <si>
-    <t>Men, Villager</t>
-  </si>
-  <si>
-    <t>Men, Witch</t>
-  </si>
-  <si>
-    <t>Men, Wizard</t>
-  </si>
-  <si>
-    <t>Men, Woodcutter</t>
-  </si>
-  <si>
-    <t>Merfaun</t>
-  </si>
-  <si>
-    <t>Merman</t>
-  </si>
-  <si>
-    <t>Mimic</t>
-  </si>
-  <si>
-    <t>Minotaur</t>
-  </si>
-  <si>
-    <t>Monkey, Flying</t>
-  </si>
-  <si>
-    <t>Mossling, Bargeman</t>
-  </si>
-  <si>
-    <t>Mossling, Mold Oracle</t>
-  </si>
-  <si>
-    <t>Mossling, Moss Gatherer</t>
-  </si>
-  <si>
-    <t>Moth, Giant Eye</t>
-  </si>
-  <si>
-    <t>Murmurin</t>
-  </si>
-  <si>
-    <t>Mushroom Men</t>
-  </si>
-  <si>
-    <t>Nack</t>
-  </si>
-  <si>
-    <t>Newt, Bog</t>
-  </si>
-  <si>
-    <t>Newt, Cave</t>
-  </si>
-  <si>
-    <t>Newt, Red</t>
-  </si>
-  <si>
-    <t>Newt, Spotted</t>
-  </si>
-  <si>
     <t>Nord Barrow</t>
   </si>
   <si>
-    <t>Nutcap</t>
-  </si>
-  <si>
-    <t>Ochre Ooze</t>
-  </si>
-  <si>
-    <t>Ogre</t>
-  </si>
-  <si>
-    <t>Orc</t>
-  </si>
-  <si>
-    <t>Orc, Cave</t>
-  </si>
-  <si>
-    <t>Otyugh</t>
-  </si>
-  <si>
-    <t>Owlbear</t>
-  </si>
-  <si>
-    <t>Peryton</t>
-  </si>
-  <si>
-    <t>Pike, Giant</t>
-  </si>
-  <si>
-    <t>Po-Wit Bird</t>
-  </si>
-  <si>
-    <t>Porcupine, Giant</t>
-  </si>
-  <si>
-    <t>Possum, Giant</t>
-  </si>
-  <si>
-    <t>Pretzel Golem</t>
-  </si>
-  <si>
-    <t>Purple Worm</t>
-  </si>
-  <si>
-    <t>Rat Swarm</t>
-  </si>
-  <si>
-    <t>Rat, Giant</t>
-  </si>
-  <si>
-    <t>Redcap</t>
-  </si>
-  <si>
-    <t>Roc</t>
-  </si>
-  <si>
-    <t>Root Thing</t>
-  </si>
-  <si>
-    <t>Roper/Piercer</t>
-  </si>
-  <si>
-    <t>Rug of Smothering</t>
-  </si>
-  <si>
-    <t>Rust Bug</t>
-  </si>
-  <si>
-    <t>Sabre-Tooth Lion</t>
-  </si>
-  <si>
-    <t>Salmon, Spike-Tooth</t>
-  </si>
-  <si>
-    <t>Scarecrow</t>
-  </si>
-  <si>
-    <t>Scorpion, Giant Cave</t>
-  </si>
-  <si>
-    <t>Scorpion, Giant Morscauda</t>
-  </si>
-  <si>
-    <t>Scorpion, Giant Tenebrarius</t>
-  </si>
-  <si>
-    <t>Selkie</t>
-  </si>
-  <si>
-    <t>Shadow Demon</t>
-  </si>
-  <si>
-    <t>Ship's Figurehead</t>
-  </si>
-  <si>
-    <t>Shrieker</t>
-  </si>
-  <si>
     <t>Skeleton</t>
   </si>
   <si>
     <t>Skeleton, Dread Knight</t>
   </si>
   <si>
-    <t>Skunk, Giant</t>
-  </si>
-  <si>
-    <t>Slug, Giant Spitting</t>
-  </si>
-  <si>
-    <t>Snail, Giant</t>
-  </si>
-  <si>
-    <t>Snake, Adder</t>
-  </si>
-  <si>
-    <t>Snake, Asp</t>
-  </si>
-  <si>
-    <t>Snake, Copperhead</t>
-  </si>
-  <si>
-    <t>Snake, Cottonmouth</t>
-  </si>
-  <si>
-    <t>Snake, Giant Copperhead</t>
-  </si>
-  <si>
-    <t>Snake, Giant Cottonmouth</t>
-  </si>
-  <si>
-    <t>Snake, Giant Timber Rattler</t>
-  </si>
-  <si>
-    <t>Snake, Giant Viper</t>
-  </si>
-  <si>
-    <t>Snake, Hoopsnake</t>
-  </si>
-  <si>
-    <t>Snake, Hypnoviper</t>
-  </si>
-  <si>
-    <t>Snake, Timber Rattler</t>
-  </si>
-  <si>
-    <t>Snake, Viper</t>
-  </si>
-  <si>
-    <t>Spider Swarm</t>
-  </si>
-  <si>
-    <t>Spider, Cave</t>
-  </si>
-  <si>
-    <t>Spider, Dark Widow</t>
-  </si>
-  <si>
-    <t>Spider, Hunter</t>
-  </si>
-  <si>
-    <t>Spider, Luteback</t>
-  </si>
-  <si>
-    <t>Spider, Tarantella</t>
-  </si>
-  <si>
-    <t>Spider, Tube</t>
-  </si>
-  <si>
-    <t>Spider, Yellow-Banded Orbweaver</t>
-  </si>
-  <si>
-    <t>Sprite</t>
-  </si>
-  <si>
-    <t>Sturgeon, Giant</t>
-  </si>
-  <si>
-    <t>Succubus Demon</t>
-  </si>
-  <si>
-    <t>Swanmay</t>
-  </si>
-  <si>
-    <t>The Hag</t>
-  </si>
-  <si>
-    <t>Treowere</t>
-  </si>
-  <si>
-    <t>Treowere, Corrupted</t>
-  </si>
-  <si>
-    <t>Troll</t>
-  </si>
-  <si>
-    <t>Troll, Moss</t>
-  </si>
-  <si>
-    <t>Troll, Mountain</t>
-  </si>
-  <si>
-    <t>Tunnel Hulk</t>
-  </si>
-  <si>
-    <t>Tunny Fish, Flying</t>
-  </si>
-  <si>
-    <t>Turtle, Giant Snapping</t>
-  </si>
-  <si>
-    <t>Turtle, River</t>
-  </si>
-  <si>
-    <t>Unicorn</t>
-  </si>
-  <si>
     <t>Vargul</t>
   </si>
   <si>
-    <t>Violet Mushroom</t>
-  </si>
-  <si>
-    <t>Vulpine</t>
-  </si>
-  <si>
     <t>Walking Corpse</t>
   </si>
   <si>
@@ -889,102 +982,9 @@
     <t>Walking Corpse, Worm-Walker</t>
   </si>
   <si>
-    <t>Walrus</t>
-  </si>
-  <si>
-    <t>Wandering Tower</t>
-  </si>
-  <si>
-    <t>Wasp, Giant Paper</t>
-  </si>
-  <si>
-    <t>Water Elemental</t>
-  </si>
-  <si>
-    <t>Water Termite, Giant</t>
-  </si>
-  <si>
-    <t>Water Weird</t>
-  </si>
-  <si>
-    <t>Wax Golem</t>
-  </si>
-  <si>
-    <t>Weasel, Giant</t>
-  </si>
-  <si>
-    <t>Weathervane Effigy</t>
-  </si>
-  <si>
-    <t>Wendigo Demon</t>
-  </si>
-  <si>
-    <t>Werebear Demon</t>
-  </si>
-  <si>
-    <t>Werewolf Demon</t>
-  </si>
-  <si>
-    <t>Whale, Oil</t>
-  </si>
-  <si>
-    <t>Whale, Tusked</t>
-  </si>
-  <si>
-    <t>Whitecap Mushroom</t>
-  </si>
-  <si>
-    <t>Wicker Golem</t>
-  </si>
-  <si>
-    <t>Wild Hunt</t>
-  </si>
-  <si>
-    <t>Wodewose</t>
-  </si>
-  <si>
-    <t>Wolf</t>
-  </si>
-  <si>
-    <t>Wolf, Corrupted</t>
-  </si>
-  <si>
     <t>Wolf, Winter</t>
   </si>
   <si>
-    <t>Wolperdingle</t>
-  </si>
-  <si>
-    <t>Wrong'un</t>
-  </si>
-  <si>
-    <t>Wyrm, Black Bile</t>
-  </si>
-  <si>
-    <t>Wyrm, Blood</t>
-  </si>
-  <si>
-    <t>Wyrm, Maegen</t>
-  </si>
-  <si>
-    <t>Wyrm, Phlegm</t>
-  </si>
-  <si>
-    <t>Wyrm, Tatzelwyrm</t>
-  </si>
-  <si>
-    <t>Wyrm, Yellow Bile</t>
-  </si>
-  <si>
-    <t>Wyvern</t>
-  </si>
-  <si>
-    <t>Yellow Mold</t>
-  </si>
-  <si>
-    <t>Yickerwill</t>
-  </si>
-  <si>
     <t>Acorns</t>
   </si>
   <si>
@@ -1156,16 +1156,10 @@
     <t>Magic Phenomena</t>
   </si>
   <si>
-    <t>Mysteries</t>
+    <t>Mysterious Occurrence</t>
   </si>
   <si>
     <t>Weather</t>
-  </si>
-  <si>
-    <t>Encounter Sign</t>
-  </si>
-  <si>
-    <t>False Encounter Sign</t>
   </si>
 </sst>
 </file>
@@ -1183,7 +1177,10 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1194,27 +1191,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -1223,9 +1205,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1244,9 +1224,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1284,7 +1264,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1318,6 +1298,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1352,9 +1333,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1528,76 +1510,82 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T364"/>
+  <dimension ref="A1:T362"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>20</v>
       </c>
-      <c r="F2">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
     </row>
@@ -1605,10 +1593,10 @@
       <c r="A3" t="s">
         <v>21</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
       <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
         <v>1</v>
       </c>
     </row>
@@ -1616,10 +1604,10 @@
       <c r="A4" t="s">
         <v>22</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
         <v>1</v>
       </c>
     </row>
@@ -1627,7 +1615,16 @@
       <c r="A5" t="s">
         <v>23</v>
       </c>
-      <c r="I5">
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
         <v>1</v>
       </c>
     </row>
@@ -1635,13 +1632,16 @@
       <c r="A6" t="s">
         <v>24</v>
       </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="D6">
+      <c r="E6">
         <v>1</v>
       </c>
       <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
         <v>1</v>
       </c>
     </row>
@@ -1649,10 +1649,19 @@
       <c r="A7" t="s">
         <v>25</v>
       </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="S7">
         <v>1</v>
       </c>
     </row>
@@ -1660,10 +1669,16 @@
       <c r="A8" t="s">
         <v>26</v>
       </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>1</v>
+      </c>
+      <c r="T8">
         <v>1</v>
       </c>
     </row>
@@ -1671,16 +1686,19 @@
       <c r="A9" t="s">
         <v>27</v>
       </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
       <c r="G9">
         <v>1</v>
       </c>
       <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>1</v>
+      </c>
+      <c r="T9">
         <v>1</v>
       </c>
     </row>
@@ -1688,16 +1706,22 @@
       <c r="A10" t="s">
         <v>28</v>
       </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
       <c r="G10">
         <v>1</v>
       </c>
       <c r="H10">
         <v>1</v>
       </c>
-      <c r="I10">
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="S10">
         <v>1</v>
       </c>
     </row>
@@ -1705,13 +1729,16 @@
       <c r="A11" t="s">
         <v>29</v>
       </c>
-      <c r="R11">
-        <v>1</v>
-      </c>
-      <c r="S11">
-        <v>1</v>
-      </c>
-      <c r="T11">
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
         <v>1</v>
       </c>
     </row>
@@ -1719,13 +1746,16 @@
       <c r="A12" t="s">
         <v>30</v>
       </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
       <c r="H12">
         <v>1</v>
       </c>
-      <c r="R12">
-        <v>1</v>
-      </c>
-      <c r="T12">
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="S12">
         <v>1</v>
       </c>
     </row>
@@ -1733,10 +1763,16 @@
       <c r="A13" t="s">
         <v>31</v>
       </c>
-      <c r="S13">
-        <v>1</v>
-      </c>
-      <c r="T13">
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="G13">
         <v>1</v>
       </c>
     </row>
@@ -1744,6 +1780,12 @@
       <c r="A14" t="s">
         <v>32</v>
       </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
       <c r="G14">
         <v>1</v>
       </c>
@@ -1751,12 +1793,6 @@
         <v>1</v>
       </c>
       <c r="I14">
-        <v>1</v>
-      </c>
-      <c r="R14">
-        <v>1</v>
-      </c>
-      <c r="S14">
         <v>1</v>
       </c>
     </row>
@@ -1764,19 +1800,16 @@
       <c r="A15" t="s">
         <v>33</v>
       </c>
-      <c r="H15">
-        <v>1</v>
-      </c>
-      <c r="J15">
-        <v>1</v>
-      </c>
-      <c r="R15">
-        <v>1</v>
-      </c>
-      <c r="S15">
-        <v>1</v>
-      </c>
-      <c r="T15">
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="P15">
         <v>1</v>
       </c>
     </row>
@@ -1784,16 +1817,13 @@
       <c r="A16" t="s">
         <v>34</v>
       </c>
-      <c r="H16">
-        <v>1</v>
-      </c>
-      <c r="R16">
-        <v>1</v>
-      </c>
-      <c r="S16">
-        <v>1</v>
-      </c>
-      <c r="T16">
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
         <v>1</v>
       </c>
     </row>
@@ -1801,19 +1831,10 @@
       <c r="A17" t="s">
         <v>35</v>
       </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-      <c r="H17">
-        <v>1</v>
-      </c>
-      <c r="R17">
-        <v>1</v>
-      </c>
-      <c r="S17">
-        <v>1</v>
-      </c>
-      <c r="T17">
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
         <v>1</v>
       </c>
     </row>
@@ -1821,22 +1842,16 @@
       <c r="A18" t="s">
         <v>36</v>
       </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
       <c r="G18">
-        <v>1</v>
-      </c>
-      <c r="H18">
-        <v>1</v>
-      </c>
-      <c r="K18">
-        <v>1</v>
-      </c>
-      <c r="L18">
-        <v>1</v>
-      </c>
-      <c r="R18">
-        <v>1</v>
-      </c>
-      <c r="S18">
         <v>1</v>
       </c>
     </row>
@@ -1844,16 +1859,19 @@
       <c r="A19" t="s">
         <v>37</v>
       </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
       <c r="D19">
         <v>1</v>
       </c>
       <c r="G19">
         <v>1</v>
       </c>
-      <c r="H19">
-        <v>1</v>
-      </c>
-      <c r="I19">
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19">
         <v>1</v>
       </c>
     </row>
@@ -1861,16 +1879,13 @@
       <c r="A20" t="s">
         <v>38</v>
       </c>
-      <c r="E20">
-        <v>1</v>
-      </c>
-      <c r="H20">
-        <v>1</v>
-      </c>
-      <c r="I20">
-        <v>1</v>
-      </c>
-      <c r="S20">
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+      <c r="P20">
         <v>1</v>
       </c>
     </row>
@@ -1878,16 +1893,10 @@
       <c r="A21" t="s">
         <v>39</v>
       </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
       <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
         <v>1</v>
       </c>
     </row>
@@ -1895,13 +1904,10 @@
       <c r="A22" t="s">
         <v>40</v>
       </c>
-      <c r="J22">
-        <v>1</v>
-      </c>
-      <c r="S22">
-        <v>1</v>
-      </c>
-      <c r="T22">
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
         <v>1</v>
       </c>
     </row>
@@ -1909,13 +1915,16 @@
       <c r="A23" t="s">
         <v>41</v>
       </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
       <c r="H23">
         <v>1</v>
       </c>
       <c r="I23">
-        <v>1</v>
-      </c>
-      <c r="J23">
         <v>1</v>
       </c>
     </row>
@@ -1923,13 +1932,13 @@
       <c r="A24" t="s">
         <v>42</v>
       </c>
-      <c r="H24">
-        <v>1</v>
-      </c>
-      <c r="I24">
-        <v>1</v>
-      </c>
-      <c r="J24">
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
         <v>1</v>
       </c>
       <c r="S24">
@@ -1940,13 +1949,13 @@
       <c r="A25" t="s">
         <v>43</v>
       </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
       <c r="H25">
-        <v>1</v>
-      </c>
-      <c r="I25">
-        <v>1</v>
-      </c>
-      <c r="J25">
         <v>1</v>
       </c>
     </row>
@@ -1954,6 +1963,12 @@
       <c r="A26" t="s">
         <v>44</v>
       </c>
+      <c r="K26">
+        <v>1</v>
+      </c>
+      <c r="L26">
+        <v>1</v>
+      </c>
       <c r="M26">
         <v>1</v>
       </c>
@@ -1962,13 +1977,13 @@
       <c r="A27" t="s">
         <v>45</v>
       </c>
-      <c r="R27">
-        <v>1</v>
-      </c>
-      <c r="S27">
-        <v>1</v>
-      </c>
-      <c r="T27">
+      <c r="K27">
+        <v>1</v>
+      </c>
+      <c r="L27">
+        <v>1</v>
+      </c>
+      <c r="P27">
         <v>1</v>
       </c>
     </row>
@@ -1976,19 +1991,10 @@
       <c r="A28" t="s">
         <v>46</v>
       </c>
-      <c r="K28">
-        <v>1</v>
-      </c>
-      <c r="L28">
-        <v>1</v>
-      </c>
-      <c r="P28">
-        <v>1</v>
-      </c>
-      <c r="R28">
-        <v>1</v>
-      </c>
-      <c r="S28">
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28">
         <v>1</v>
       </c>
     </row>
@@ -1996,6 +2002,9 @@
       <c r="A29" t="s">
         <v>47</v>
       </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
       <c r="R29">
         <v>1</v>
       </c>
@@ -2010,16 +2019,13 @@
       <c r="A30" t="s">
         <v>48</v>
       </c>
-      <c r="B30">
-        <v>1</v>
-      </c>
       <c r="D30">
         <v>1</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
-      <c r="G30">
+      <c r="F30">
         <v>1</v>
       </c>
     </row>
@@ -2027,19 +2033,16 @@
       <c r="A31" t="s">
         <v>49</v>
       </c>
-      <c r="D31">
-        <v>1</v>
-      </c>
       <c r="E31">
         <v>1</v>
       </c>
       <c r="G31">
         <v>1</v>
       </c>
-      <c r="H31">
-        <v>1</v>
-      </c>
-      <c r="I31">
+      <c r="R31">
+        <v>1</v>
+      </c>
+      <c r="S31">
         <v>1</v>
       </c>
     </row>
@@ -2064,13 +2067,10 @@
       <c r="A33" t="s">
         <v>51</v>
       </c>
-      <c r="G33">
-        <v>1</v>
-      </c>
-      <c r="H33">
-        <v>1</v>
-      </c>
-      <c r="I33">
+      <c r="M33">
+        <v>1</v>
+      </c>
+      <c r="N33">
         <v>1</v>
       </c>
     </row>
@@ -2078,16 +2078,13 @@
       <c r="A34" t="s">
         <v>52</v>
       </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
       <c r="E34">
-        <v>1</v>
-      </c>
-      <c r="G34">
-        <v>1</v>
-      </c>
-      <c r="H34">
-        <v>1</v>
-      </c>
-      <c r="I34">
         <v>1</v>
       </c>
     </row>
@@ -2095,19 +2092,16 @@
       <c r="A35" t="s">
         <v>53</v>
       </c>
-      <c r="C35">
-        <v>1</v>
-      </c>
-      <c r="D35">
+      <c r="E35">
         <v>1</v>
       </c>
       <c r="G35">
         <v>1</v>
       </c>
-      <c r="O35">
-        <v>1</v>
-      </c>
-      <c r="Q35">
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35">
         <v>1</v>
       </c>
     </row>
@@ -2115,19 +2109,10 @@
       <c r="A36" t="s">
         <v>54</v>
       </c>
-      <c r="C36">
-        <v>1</v>
-      </c>
-      <c r="D36">
-        <v>1</v>
-      </c>
-      <c r="G36">
-        <v>1</v>
-      </c>
-      <c r="O36">
-        <v>1</v>
-      </c>
-      <c r="Q36">
+      <c r="S36">
+        <v>1</v>
+      </c>
+      <c r="T36">
         <v>1</v>
       </c>
     </row>
@@ -2135,13 +2120,10 @@
       <c r="A37" t="s">
         <v>55</v>
       </c>
-      <c r="Q37">
-        <v>1</v>
-      </c>
-      <c r="R37">
-        <v>1</v>
-      </c>
-      <c r="T37">
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="D37">
         <v>1</v>
       </c>
     </row>
@@ -2149,13 +2131,10 @@
       <c r="A38" t="s">
         <v>56</v>
       </c>
-      <c r="J38">
-        <v>1</v>
-      </c>
-      <c r="S38">
-        <v>1</v>
-      </c>
-      <c r="T38">
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="D38">
         <v>1</v>
       </c>
     </row>
@@ -2163,16 +2142,16 @@
       <c r="A39" t="s">
         <v>57</v>
       </c>
-      <c r="H39">
-        <v>1</v>
-      </c>
-      <c r="L39">
-        <v>1</v>
-      </c>
-      <c r="S39">
-        <v>1</v>
-      </c>
-      <c r="T39">
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+      <c r="G39">
         <v>1</v>
       </c>
     </row>
@@ -2180,16 +2159,13 @@
       <c r="A40" t="s">
         <v>58</v>
       </c>
-      <c r="K40">
-        <v>1</v>
-      </c>
-      <c r="L40">
-        <v>1</v>
-      </c>
-      <c r="M40">
-        <v>1</v>
-      </c>
-      <c r="P40">
+      <c r="H40">
+        <v>1</v>
+      </c>
+      <c r="I40">
+        <v>1</v>
+      </c>
+      <c r="J40">
         <v>1</v>
       </c>
     </row>
@@ -2197,13 +2173,10 @@
       <c r="A41" t="s">
         <v>59</v>
       </c>
+      <c r="B41">
+        <v>1</v>
+      </c>
       <c r="D41">
-        <v>1</v>
-      </c>
-      <c r="E41">
-        <v>1</v>
-      </c>
-      <c r="F41">
         <v>1</v>
       </c>
     </row>
@@ -2211,10 +2184,13 @@
       <c r="A42" t="s">
         <v>60</v>
       </c>
-      <c r="K42">
-        <v>1</v>
-      </c>
-      <c r="L42">
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="D42">
+        <v>1</v>
+      </c>
+      <c r="E42">
         <v>1</v>
       </c>
     </row>
@@ -2222,10 +2198,22 @@
       <c r="A43" t="s">
         <v>61</v>
       </c>
-      <c r="S43">
-        <v>1</v>
-      </c>
-      <c r="T43">
+      <c r="E43">
+        <v>1</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+      <c r="H43">
+        <v>1</v>
+      </c>
+      <c r="I43">
+        <v>1</v>
+      </c>
+      <c r="L43">
         <v>1</v>
       </c>
     </row>
@@ -2236,10 +2224,7 @@
       <c r="B44">
         <v>1</v>
       </c>
-      <c r="D44">
-        <v>1</v>
-      </c>
-      <c r="G44">
+      <c r="K44">
         <v>1</v>
       </c>
     </row>
@@ -2247,28 +2232,13 @@
       <c r="A45" t="s">
         <v>63</v>
       </c>
-      <c r="D45">
+      <c r="B45">
         <v>1</v>
       </c>
       <c r="G45">
         <v>1</v>
       </c>
       <c r="H45">
-        <v>1</v>
-      </c>
-      <c r="I45">
-        <v>1</v>
-      </c>
-      <c r="J45">
-        <v>1</v>
-      </c>
-      <c r="R45">
-        <v>1</v>
-      </c>
-      <c r="S45">
-        <v>1</v>
-      </c>
-      <c r="T45">
         <v>1</v>
       </c>
     </row>
@@ -2276,16 +2246,16 @@
       <c r="A46" t="s">
         <v>64</v>
       </c>
-      <c r="G46">
-        <v>1</v>
-      </c>
-      <c r="H46">
-        <v>1</v>
-      </c>
-      <c r="I46">
-        <v>1</v>
-      </c>
-      <c r="J46">
+      <c r="D46">
+        <v>1</v>
+      </c>
+      <c r="E46">
+        <v>1</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="R46">
         <v>1</v>
       </c>
       <c r="S46">
@@ -2296,24 +2266,6 @@
       <c r="A47" t="s">
         <v>65</v>
       </c>
-      <c r="B47">
-        <v>1</v>
-      </c>
-      <c r="D47">
-        <v>1</v>
-      </c>
-      <c r="G47">
-        <v>1</v>
-      </c>
-      <c r="H47">
-        <v>1</v>
-      </c>
-      <c r="I47">
-        <v>1</v>
-      </c>
-      <c r="J47">
-        <v>1</v>
-      </c>
       <c r="R47">
         <v>1</v>
       </c>
@@ -2328,15 +2280,6 @@
       <c r="A48" t="s">
         <v>66</v>
       </c>
-      <c r="D48">
-        <v>1</v>
-      </c>
-      <c r="E48">
-        <v>1</v>
-      </c>
-      <c r="F48">
-        <v>1</v>
-      </c>
       <c r="G48">
         <v>1</v>
       </c>
@@ -2345,13 +2288,13 @@
       <c r="A49" t="s">
         <v>67</v>
       </c>
-      <c r="Q49">
-        <v>1</v>
-      </c>
-      <c r="R49">
-        <v>1</v>
-      </c>
-      <c r="T49">
+      <c r="G49">
+        <v>1</v>
+      </c>
+      <c r="H49">
+        <v>1</v>
+      </c>
+      <c r="I49">
         <v>1</v>
       </c>
     </row>
@@ -2359,13 +2302,13 @@
       <c r="A50" t="s">
         <v>68</v>
       </c>
-      <c r="B50">
-        <v>1</v>
-      </c>
-      <c r="D50">
-        <v>1</v>
-      </c>
-      <c r="G50">
+      <c r="E50">
+        <v>1</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+      <c r="R50">
         <v>1</v>
       </c>
     </row>
@@ -2373,19 +2316,10 @@
       <c r="A51" t="s">
         <v>69</v>
       </c>
-      <c r="B51">
-        <v>1</v>
-      </c>
-      <c r="D51">
-        <v>1</v>
-      </c>
-      <c r="G51">
-        <v>1</v>
-      </c>
-      <c r="K51">
-        <v>1</v>
-      </c>
-      <c r="L51">
+      <c r="M51">
+        <v>1</v>
+      </c>
+      <c r="P51">
         <v>1</v>
       </c>
     </row>
@@ -2393,10 +2327,13 @@
       <c r="A52" t="s">
         <v>70</v>
       </c>
-      <c r="B52">
-        <v>1</v>
-      </c>
-      <c r="N52">
+      <c r="G52">
+        <v>1</v>
+      </c>
+      <c r="H52">
+        <v>1</v>
+      </c>
+      <c r="R52">
         <v>1</v>
       </c>
     </row>
@@ -2407,16 +2344,13 @@
       <c r="B53">
         <v>1</v>
       </c>
-      <c r="K53">
-        <v>1</v>
-      </c>
-      <c r="M53">
-        <v>1</v>
-      </c>
-      <c r="N53">
-        <v>1</v>
-      </c>
-      <c r="P53">
+      <c r="D53">
+        <v>1</v>
+      </c>
+      <c r="G53">
+        <v>1</v>
+      </c>
+      <c r="H53">
         <v>1</v>
       </c>
     </row>
@@ -2424,10 +2358,16 @@
       <c r="A54" t="s">
         <v>72</v>
       </c>
-      <c r="M54">
-        <v>1</v>
-      </c>
-      <c r="P54">
+      <c r="G54">
+        <v>1</v>
+      </c>
+      <c r="H54">
+        <v>1</v>
+      </c>
+      <c r="K54">
+        <v>1</v>
+      </c>
+      <c r="L54">
         <v>1</v>
       </c>
     </row>
@@ -2435,7 +2375,10 @@
       <c r="A55" t="s">
         <v>73</v>
       </c>
-      <c r="N55">
+      <c r="S55">
+        <v>1</v>
+      </c>
+      <c r="T55">
         <v>1</v>
       </c>
     </row>
@@ -2443,10 +2386,16 @@
       <c r="A56" t="s">
         <v>74</v>
       </c>
-      <c r="M56">
-        <v>1</v>
-      </c>
-      <c r="P56">
+      <c r="Q56">
+        <v>1</v>
+      </c>
+      <c r="R56">
+        <v>1</v>
+      </c>
+      <c r="S56">
+        <v>1</v>
+      </c>
+      <c r="T56">
         <v>1</v>
       </c>
     </row>
@@ -2454,13 +2403,7 @@
       <c r="A57" t="s">
         <v>75</v>
       </c>
-      <c r="M57">
-        <v>1</v>
-      </c>
-      <c r="P57">
-        <v>1</v>
-      </c>
-      <c r="S57">
+      <c r="F57">
         <v>1</v>
       </c>
     </row>
@@ -2468,13 +2411,13 @@
       <c r="A58" t="s">
         <v>76</v>
       </c>
-      <c r="K58">
-        <v>1</v>
-      </c>
-      <c r="L58">
-        <v>1</v>
-      </c>
-      <c r="P58">
+      <c r="D58">
+        <v>1</v>
+      </c>
+      <c r="E58">
+        <v>1</v>
+      </c>
+      <c r="G58">
         <v>1</v>
       </c>
     </row>
@@ -2482,19 +2425,7 @@
       <c r="A59" t="s">
         <v>77</v>
       </c>
-      <c r="K59">
-        <v>1</v>
-      </c>
-      <c r="L59">
-        <v>1</v>
-      </c>
       <c r="P59">
-        <v>1</v>
-      </c>
-      <c r="S59">
-        <v>1</v>
-      </c>
-      <c r="T59">
         <v>1</v>
       </c>
     </row>
@@ -2502,6 +2433,12 @@
       <c r="A60" t="s">
         <v>78</v>
       </c>
+      <c r="B60">
+        <v>1</v>
+      </c>
+      <c r="D60">
+        <v>1</v>
+      </c>
       <c r="G60">
         <v>1</v>
       </c>
@@ -2513,10 +2450,25 @@
       <c r="A61" t="s">
         <v>79</v>
       </c>
+      <c r="B61">
+        <v>1</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
+      <c r="D61">
+        <v>1</v>
+      </c>
+      <c r="E61">
+        <v>1</v>
+      </c>
       <c r="G61">
         <v>1</v>
       </c>
       <c r="H61">
+        <v>1</v>
+      </c>
+      <c r="K61">
         <v>1</v>
       </c>
     </row>
@@ -2524,10 +2476,13 @@
       <c r="A62" t="s">
         <v>80</v>
       </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="D62">
+        <v>1</v>
+      </c>
       <c r="G62">
-        <v>1</v>
-      </c>
-      <c r="H62">
         <v>1</v>
       </c>
     </row>
@@ -2535,16 +2490,16 @@
       <c r="A63" t="s">
         <v>81</v>
       </c>
-      <c r="E63">
+      <c r="B63">
+        <v>1</v>
+      </c>
+      <c r="D63">
         <v>1</v>
       </c>
       <c r="G63">
         <v>1</v>
       </c>
       <c r="H63">
-        <v>1</v>
-      </c>
-      <c r="I63">
         <v>1</v>
       </c>
     </row>
@@ -2552,20 +2507,17 @@
       <c r="A64" t="s">
         <v>82</v>
       </c>
-      <c r="D64">
-        <v>1</v>
-      </c>
-      <c r="E64">
-        <v>1</v>
-      </c>
-      <c r="F64">
-        <v>1</v>
-      </c>
-      <c r="S64">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="K64">
+        <v>1</v>
+      </c>
+      <c r="L64">
+        <v>1</v>
+      </c>
+      <c r="P64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>83</v>
       </c>
@@ -2578,224 +2530,191 @@
       <c r="G65">
         <v>1</v>
       </c>
-      <c r="K65">
-        <v>1</v>
-      </c>
-      <c r="L65">
-        <v>1</v>
-      </c>
-      <c r="R65">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="H65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>84</v>
       </c>
-      <c r="C66">
-        <v>1</v>
-      </c>
-      <c r="E66">
-        <v>1</v>
-      </c>
-      <c r="O66">
-        <v>1</v>
-      </c>
-      <c r="Q66">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="K66">
+        <v>1</v>
+      </c>
+      <c r="L66">
+        <v>1</v>
+      </c>
+      <c r="P66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>85</v>
       </c>
-      <c r="C67">
-        <v>1</v>
-      </c>
       <c r="D67">
         <v>1</v>
       </c>
       <c r="E67">
         <v>1</v>
       </c>
-      <c r="F67">
-        <v>1</v>
-      </c>
-      <c r="O67">
-        <v>1</v>
-      </c>
-      <c r="Q67">
-        <v>1</v>
-      </c>
-      <c r="R67">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="G67">
+        <v>1</v>
+      </c>
+      <c r="H67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>86</v>
       </c>
-      <c r="C68">
-        <v>1</v>
-      </c>
-      <c r="E68">
-        <v>1</v>
-      </c>
-      <c r="O68">
-        <v>1</v>
-      </c>
-      <c r="Q68">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="D68">
+        <v>1</v>
+      </c>
+      <c r="G68">
+        <v>1</v>
+      </c>
+      <c r="H68">
+        <v>1</v>
+      </c>
+      <c r="I68">
+        <v>1</v>
+      </c>
+      <c r="J68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>87</v>
       </c>
-      <c r="C69">
+      <c r="B69">
+        <v>1</v>
+      </c>
+      <c r="D69">
         <v>1</v>
       </c>
       <c r="E69">
         <v>1</v>
       </c>
-      <c r="O69">
-        <v>1</v>
-      </c>
-      <c r="Q69">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.45">
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>88</v>
       </c>
-      <c r="C70">
-        <v>1</v>
-      </c>
       <c r="E70">
         <v>1</v>
       </c>
-      <c r="O70">
-        <v>1</v>
-      </c>
-      <c r="Q70">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="G70">
+        <v>1</v>
+      </c>
+      <c r="H70">
+        <v>1</v>
+      </c>
+      <c r="I70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>89</v>
       </c>
-      <c r="C71">
+      <c r="D71">
         <v>1</v>
       </c>
       <c r="E71">
         <v>1</v>
       </c>
-      <c r="O71">
-        <v>1</v>
-      </c>
-      <c r="Q71">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="G71">
+        <v>1</v>
+      </c>
+      <c r="H71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>90</v>
       </c>
-      <c r="E72">
-        <v>1</v>
-      </c>
-      <c r="F72">
-        <v>1</v>
-      </c>
-      <c r="S72">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="D72">
+        <v>1</v>
+      </c>
+      <c r="G72">
+        <v>1</v>
+      </c>
+      <c r="H72">
+        <v>1</v>
+      </c>
+      <c r="I72">
+        <v>1</v>
+      </c>
+      <c r="J72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>91</v>
       </c>
-      <c r="Q73">
-        <v>1</v>
-      </c>
-      <c r="R73">
-        <v>1</v>
-      </c>
-      <c r="T73">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="M73">
+        <v>1</v>
+      </c>
+      <c r="P73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>92</v>
       </c>
-      <c r="Q74">
-        <v>1</v>
-      </c>
-      <c r="R74">
-        <v>1</v>
-      </c>
-      <c r="T74">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="N74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>93</v>
       </c>
-      <c r="G75">
-        <v>1</v>
-      </c>
-      <c r="H75">
-        <v>1</v>
-      </c>
-      <c r="I75">
-        <v>1</v>
-      </c>
-      <c r="R75">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="M75">
+        <v>1</v>
+      </c>
+      <c r="P75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>94</v>
       </c>
-      <c r="G76">
-        <v>1</v>
-      </c>
-      <c r="H76">
-        <v>1</v>
-      </c>
-      <c r="I76">
-        <v>1</v>
-      </c>
-      <c r="R76">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="K76">
+        <v>1</v>
+      </c>
+      <c r="L76">
+        <v>1</v>
+      </c>
+      <c r="M76">
+        <v>1</v>
+      </c>
+      <c r="P76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>95</v>
       </c>
-      <c r="G77">
-        <v>1</v>
-      </c>
-      <c r="H77">
-        <v>1</v>
-      </c>
-      <c r="I77">
-        <v>1</v>
-      </c>
-      <c r="R77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="N77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>96</v>
       </c>
+      <c r="B78">
+        <v>1</v>
+      </c>
       <c r="D78">
         <v>1</v>
       </c>
@@ -2805,41 +2724,20 @@
       <c r="H78">
         <v>1</v>
       </c>
-      <c r="I78">
-        <v>1</v>
-      </c>
-      <c r="R78">
-        <v>1</v>
-      </c>
-      <c r="S78">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.45">
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>97</v>
       </c>
-      <c r="D79">
-        <v>1</v>
-      </c>
-      <c r="G79">
-        <v>1</v>
-      </c>
-      <c r="H79">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="N79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>98</v>
       </c>
-      <c r="Q80">
-        <v>1</v>
-      </c>
-      <c r="R80">
-        <v>1</v>
-      </c>
-      <c r="T80">
+      <c r="N80">
         <v>1</v>
       </c>
     </row>
@@ -2847,13 +2745,16 @@
       <c r="A81" t="s">
         <v>99</v>
       </c>
-      <c r="C81">
-        <v>1</v>
-      </c>
-      <c r="Q81">
-        <v>1</v>
-      </c>
-      <c r="R81">
+      <c r="D81">
+        <v>1</v>
+      </c>
+      <c r="E81">
+        <v>1</v>
+      </c>
+      <c r="G81">
+        <v>1</v>
+      </c>
+      <c r="H81">
         <v>1</v>
       </c>
     </row>
@@ -2861,13 +2762,10 @@
       <c r="A82" t="s">
         <v>100</v>
       </c>
-      <c r="F82">
-        <v>1</v>
-      </c>
-      <c r="R82">
-        <v>1</v>
-      </c>
-      <c r="S82">
+      <c r="B82">
+        <v>1</v>
+      </c>
+      <c r="D82">
         <v>1</v>
       </c>
     </row>
@@ -2875,19 +2773,19 @@
       <c r="A83" t="s">
         <v>101</v>
       </c>
-      <c r="G83">
-        <v>1</v>
-      </c>
       <c r="H83">
         <v>1</v>
       </c>
-      <c r="I83">
-        <v>1</v>
-      </c>
       <c r="J83">
         <v>1</v>
       </c>
-      <c r="L83">
+      <c r="R83">
+        <v>1</v>
+      </c>
+      <c r="S83">
+        <v>1</v>
+      </c>
+      <c r="T83">
         <v>1</v>
       </c>
     </row>
@@ -2898,19 +2796,13 @@
       <c r="B84">
         <v>1</v>
       </c>
+      <c r="C84">
+        <v>1</v>
+      </c>
       <c r="D84">
         <v>1</v>
       </c>
       <c r="G84">
-        <v>1</v>
-      </c>
-      <c r="K84">
-        <v>1</v>
-      </c>
-      <c r="L84">
-        <v>1</v>
-      </c>
-      <c r="R84">
         <v>1</v>
       </c>
     </row>
@@ -2918,22 +2810,13 @@
       <c r="A85" t="s">
         <v>103</v>
       </c>
-      <c r="B85">
-        <v>1</v>
-      </c>
-      <c r="D85">
-        <v>1</v>
-      </c>
-      <c r="G85">
-        <v>1</v>
-      </c>
-      <c r="K85">
-        <v>1</v>
-      </c>
-      <c r="L85">
-        <v>1</v>
-      </c>
-      <c r="R85">
+      <c r="J85">
+        <v>1</v>
+      </c>
+      <c r="S85">
+        <v>1</v>
+      </c>
+      <c r="T85">
         <v>1</v>
       </c>
     </row>
@@ -2941,22 +2824,13 @@
       <c r="A86" t="s">
         <v>104</v>
       </c>
-      <c r="B86">
-        <v>1</v>
-      </c>
-      <c r="D86">
-        <v>1</v>
-      </c>
-      <c r="E86">
-        <v>1</v>
-      </c>
-      <c r="G86">
-        <v>1</v>
-      </c>
-      <c r="K86">
-        <v>1</v>
-      </c>
-      <c r="L86">
+      <c r="H86">
+        <v>1</v>
+      </c>
+      <c r="I86">
+        <v>1</v>
+      </c>
+      <c r="J86">
         <v>1</v>
       </c>
     </row>
@@ -2964,22 +2838,16 @@
       <c r="A87" t="s">
         <v>105</v>
       </c>
-      <c r="B87">
-        <v>1</v>
-      </c>
-      <c r="G87">
-        <v>1</v>
-      </c>
-      <c r="K87">
-        <v>1</v>
-      </c>
-      <c r="L87">
-        <v>1</v>
-      </c>
-      <c r="M87">
-        <v>1</v>
-      </c>
-      <c r="P87">
+      <c r="H87">
+        <v>1</v>
+      </c>
+      <c r="I87">
+        <v>1</v>
+      </c>
+      <c r="J87">
+        <v>1</v>
+      </c>
+      <c r="S87">
         <v>1</v>
       </c>
     </row>
@@ -2987,13 +2855,13 @@
       <c r="A88" t="s">
         <v>106</v>
       </c>
-      <c r="K88">
-        <v>1</v>
-      </c>
-      <c r="L88">
-        <v>1</v>
-      </c>
-      <c r="M88">
+      <c r="H88">
+        <v>1</v>
+      </c>
+      <c r="I88">
+        <v>1</v>
+      </c>
+      <c r="J88">
         <v>1</v>
       </c>
     </row>
@@ -3001,13 +2869,16 @@
       <c r="A89" t="s">
         <v>107</v>
       </c>
-      <c r="C89">
-        <v>1</v>
-      </c>
-      <c r="O89">
-        <v>1</v>
-      </c>
-      <c r="R89">
+      <c r="H89">
+        <v>1</v>
+      </c>
+      <c r="L89">
+        <v>1</v>
+      </c>
+      <c r="S89">
+        <v>1</v>
+      </c>
+      <c r="T89">
         <v>1</v>
       </c>
     </row>
@@ -3015,13 +2886,10 @@
       <c r="A90" t="s">
         <v>108</v>
       </c>
-      <c r="K90">
-        <v>1</v>
-      </c>
-      <c r="L90">
-        <v>1</v>
-      </c>
-      <c r="P90">
+      <c r="S90">
+        <v>1</v>
+      </c>
+      <c r="T90">
         <v>1</v>
       </c>
     </row>
@@ -3029,10 +2897,25 @@
       <c r="A91" t="s">
         <v>109</v>
       </c>
-      <c r="Q91">
+      <c r="D91">
+        <v>1</v>
+      </c>
+      <c r="G91">
+        <v>1</v>
+      </c>
+      <c r="H91">
+        <v>1</v>
+      </c>
+      <c r="I91">
+        <v>1</v>
+      </c>
+      <c r="J91">
         <v>1</v>
       </c>
       <c r="R91">
+        <v>1</v>
+      </c>
+      <c r="S91">
         <v>1</v>
       </c>
       <c r="T91">
@@ -3043,6 +2926,9 @@
       <c r="A92" t="s">
         <v>110</v>
       </c>
+      <c r="G92">
+        <v>1</v>
+      </c>
       <c r="H92">
         <v>1</v>
       </c>
@@ -3052,13 +2938,7 @@
       <c r="J92">
         <v>1</v>
       </c>
-      <c r="L92">
-        <v>1</v>
-      </c>
       <c r="S92">
-        <v>1</v>
-      </c>
-      <c r="T92">
         <v>1</v>
       </c>
     </row>
@@ -3066,6 +2946,24 @@
       <c r="A93" t="s">
         <v>111</v>
       </c>
+      <c r="B93">
+        <v>1</v>
+      </c>
+      <c r="D93">
+        <v>1</v>
+      </c>
+      <c r="G93">
+        <v>1</v>
+      </c>
+      <c r="H93">
+        <v>1</v>
+      </c>
+      <c r="I93">
+        <v>1</v>
+      </c>
+      <c r="J93">
+        <v>1</v>
+      </c>
       <c r="R93">
         <v>1</v>
       </c>
@@ -3080,16 +2978,10 @@
       <c r="A94" t="s">
         <v>112</v>
       </c>
-      <c r="H94">
-        <v>1</v>
-      </c>
-      <c r="I94">
-        <v>1</v>
-      </c>
-      <c r="R94">
-        <v>1</v>
-      </c>
-      <c r="S94">
+      <c r="B94">
+        <v>1</v>
+      </c>
+      <c r="N94">
         <v>1</v>
       </c>
     </row>
@@ -3097,10 +2989,19 @@
       <c r="A95" t="s">
         <v>113</v>
       </c>
-      <c r="R95">
-        <v>1</v>
-      </c>
-      <c r="T95">
+      <c r="B95">
+        <v>1</v>
+      </c>
+      <c r="K95">
+        <v>1</v>
+      </c>
+      <c r="M95">
+        <v>1</v>
+      </c>
+      <c r="N95">
+        <v>1</v>
+      </c>
+      <c r="P95">
         <v>1</v>
       </c>
     </row>
@@ -3108,16 +3009,10 @@
       <c r="A96" t="s">
         <v>114</v>
       </c>
-      <c r="C96">
-        <v>1</v>
-      </c>
-      <c r="D96">
-        <v>1</v>
-      </c>
-      <c r="O96">
-        <v>1</v>
-      </c>
-      <c r="R96">
+      <c r="M96">
+        <v>1</v>
+      </c>
+      <c r="P96">
         <v>1</v>
       </c>
     </row>
@@ -3125,16 +3020,7 @@
       <c r="A97" t="s">
         <v>115</v>
       </c>
-      <c r="O97">
-        <v>1</v>
-      </c>
-      <c r="Q97">
-        <v>1</v>
-      </c>
-      <c r="R97">
-        <v>1</v>
-      </c>
-      <c r="T97">
+      <c r="N97">
         <v>1</v>
       </c>
     </row>
@@ -3142,10 +3028,10 @@
       <c r="A98" t="s">
         <v>116</v>
       </c>
-      <c r="K98">
-        <v>1</v>
-      </c>
-      <c r="L98">
+      <c r="M98">
+        <v>1</v>
+      </c>
+      <c r="P98">
         <v>1</v>
       </c>
     </row>
@@ -3153,10 +3039,13 @@
       <c r="A99" t="s">
         <v>117</v>
       </c>
-      <c r="R99">
-        <v>1</v>
-      </c>
-      <c r="T99">
+      <c r="M99">
+        <v>1</v>
+      </c>
+      <c r="P99">
+        <v>1</v>
+      </c>
+      <c r="S99">
         <v>1</v>
       </c>
     </row>
@@ -3164,7 +3053,7 @@
       <c r="A100" t="s">
         <v>118</v>
       </c>
-      <c r="C100">
+      <c r="B100">
         <v>1</v>
       </c>
       <c r="D100">
@@ -3173,7 +3062,10 @@
       <c r="G100">
         <v>1</v>
       </c>
-      <c r="O100">
+      <c r="K100">
+        <v>1</v>
+      </c>
+      <c r="L100">
         <v>1</v>
       </c>
       <c r="R100">
@@ -3184,19 +3076,19 @@
       <c r="A101" t="s">
         <v>119</v>
       </c>
-      <c r="C101">
-        <v>1</v>
-      </c>
-      <c r="O101">
-        <v>1</v>
-      </c>
-      <c r="Q101">
-        <v>1</v>
-      </c>
-      <c r="R101">
-        <v>1</v>
-      </c>
-      <c r="T101">
+      <c r="G101">
+        <v>1</v>
+      </c>
+      <c r="H101">
+        <v>1</v>
+      </c>
+      <c r="I101">
+        <v>1</v>
+      </c>
+      <c r="J101">
+        <v>1</v>
+      </c>
+      <c r="L101">
         <v>1</v>
       </c>
     </row>
@@ -3204,13 +3096,22 @@
       <c r="A102" t="s">
         <v>120</v>
       </c>
+      <c r="B102">
+        <v>1</v>
+      </c>
       <c r="D102">
         <v>1</v>
       </c>
-      <c r="E102">
-        <v>1</v>
-      </c>
-      <c r="F102">
+      <c r="G102">
+        <v>1</v>
+      </c>
+      <c r="K102">
+        <v>1</v>
+      </c>
+      <c r="L102">
+        <v>1</v>
+      </c>
+      <c r="R102">
         <v>1</v>
       </c>
     </row>
@@ -3218,13 +3119,22 @@
       <c r="A103" t="s">
         <v>121</v>
       </c>
+      <c r="B103">
+        <v>1</v>
+      </c>
       <c r="D103">
         <v>1</v>
       </c>
-      <c r="E103">
-        <v>1</v>
-      </c>
-      <c r="F103">
+      <c r="G103">
+        <v>1</v>
+      </c>
+      <c r="K103">
+        <v>1</v>
+      </c>
+      <c r="L103">
+        <v>1</v>
+      </c>
+      <c r="R103">
         <v>1</v>
       </c>
     </row>
@@ -3232,7 +3142,22 @@
       <c r="A104" t="s">
         <v>122</v>
       </c>
-      <c r="S104">
+      <c r="B104">
+        <v>1</v>
+      </c>
+      <c r="D104">
+        <v>1</v>
+      </c>
+      <c r="E104">
+        <v>1</v>
+      </c>
+      <c r="G104">
+        <v>1</v>
+      </c>
+      <c r="K104">
+        <v>1</v>
+      </c>
+      <c r="L104">
         <v>1</v>
       </c>
     </row>
@@ -3240,7 +3165,22 @@
       <c r="A105" t="s">
         <v>123</v>
       </c>
-      <c r="F105">
+      <c r="B105">
+        <v>1</v>
+      </c>
+      <c r="G105">
+        <v>1</v>
+      </c>
+      <c r="K105">
+        <v>1</v>
+      </c>
+      <c r="L105">
+        <v>1</v>
+      </c>
+      <c r="M105">
+        <v>1</v>
+      </c>
+      <c r="P105">
         <v>1</v>
       </c>
     </row>
@@ -3248,16 +3188,16 @@
       <c r="A106" t="s">
         <v>124</v>
       </c>
-      <c r="G106">
-        <v>1</v>
-      </c>
-      <c r="H106">
-        <v>1</v>
-      </c>
-      <c r="Q106">
-        <v>1</v>
-      </c>
-      <c r="R106">
+      <c r="K106">
+        <v>1</v>
+      </c>
+      <c r="L106">
+        <v>1</v>
+      </c>
+      <c r="M106">
+        <v>1</v>
+      </c>
+      <c r="P106">
         <v>1</v>
       </c>
     </row>
@@ -3265,13 +3205,16 @@
       <c r="A107" t="s">
         <v>125</v>
       </c>
-      <c r="Q107">
-        <v>1</v>
-      </c>
-      <c r="R107">
-        <v>1</v>
-      </c>
-      <c r="T107">
+      <c r="K107">
+        <v>1</v>
+      </c>
+      <c r="L107">
+        <v>1</v>
+      </c>
+      <c r="M107">
+        <v>1</v>
+      </c>
+      <c r="P107">
         <v>1</v>
       </c>
     </row>
@@ -3279,13 +3222,16 @@
       <c r="A108" t="s">
         <v>126</v>
       </c>
-      <c r="O108">
-        <v>1</v>
-      </c>
-      <c r="Q108">
+      <c r="G108">
         <v>1</v>
       </c>
       <c r="R108">
+        <v>1</v>
+      </c>
+      <c r="S108">
+        <v>1</v>
+      </c>
+      <c r="T108">
         <v>1</v>
       </c>
     </row>
@@ -3293,10 +3239,16 @@
       <c r="A109" t="s">
         <v>127</v>
       </c>
-      <c r="E109">
-        <v>1</v>
-      </c>
-      <c r="F109">
+      <c r="G109">
+        <v>1</v>
+      </c>
+      <c r="H109">
+        <v>1</v>
+      </c>
+      <c r="I109">
+        <v>1</v>
+      </c>
+      <c r="R109">
         <v>1</v>
       </c>
     </row>
@@ -3304,25 +3256,16 @@
       <c r="A110" t="s">
         <v>128</v>
       </c>
-      <c r="C110">
-        <v>1</v>
-      </c>
-      <c r="G110">
-        <v>1</v>
-      </c>
-      <c r="H110">
-        <v>1</v>
-      </c>
-      <c r="I110">
-        <v>1</v>
-      </c>
-      <c r="O110">
-        <v>1</v>
-      </c>
-      <c r="Q110">
-        <v>1</v>
-      </c>
-      <c r="R110">
+      <c r="K110">
+        <v>1</v>
+      </c>
+      <c r="L110">
+        <v>1</v>
+      </c>
+      <c r="M110">
+        <v>1</v>
+      </c>
+      <c r="P110">
         <v>1</v>
       </c>
     </row>
@@ -3330,25 +3273,7 @@
       <c r="A111" t="s">
         <v>129</v>
       </c>
-      <c r="C111">
-        <v>1</v>
-      </c>
-      <c r="G111">
-        <v>1</v>
-      </c>
-      <c r="H111">
-        <v>1</v>
-      </c>
-      <c r="I111">
-        <v>1</v>
-      </c>
-      <c r="O111">
-        <v>1</v>
-      </c>
-      <c r="Q111">
-        <v>1</v>
-      </c>
-      <c r="R111">
+      <c r="S111">
         <v>1</v>
       </c>
     </row>
@@ -3356,25 +3281,22 @@
       <c r="A112" t="s">
         <v>130</v>
       </c>
-      <c r="C112">
-        <v>1</v>
-      </c>
       <c r="G112">
         <v>1</v>
       </c>
       <c r="H112">
         <v>1</v>
       </c>
-      <c r="I112">
-        <v>1</v>
-      </c>
-      <c r="O112">
-        <v>1</v>
-      </c>
-      <c r="Q112">
-        <v>1</v>
-      </c>
-      <c r="R112">
+      <c r="K112">
+        <v>1</v>
+      </c>
+      <c r="L112">
+        <v>1</v>
+      </c>
+      <c r="M112">
+        <v>1</v>
+      </c>
+      <c r="P112">
         <v>1</v>
       </c>
     </row>
@@ -3382,16 +3304,19 @@
       <c r="A113" t="s">
         <v>131</v>
       </c>
-      <c r="L113">
-        <v>1</v>
-      </c>
-      <c r="R113">
-        <v>1</v>
-      </c>
-      <c r="S113">
-        <v>1</v>
-      </c>
-      <c r="T113">
+      <c r="D113">
+        <v>1</v>
+      </c>
+      <c r="G113">
+        <v>1</v>
+      </c>
+      <c r="H113">
+        <v>1</v>
+      </c>
+      <c r="K113">
+        <v>1</v>
+      </c>
+      <c r="P113">
         <v>1</v>
       </c>
     </row>
@@ -3399,7 +3324,7 @@
       <c r="A114" t="s">
         <v>132</v>
       </c>
-      <c r="E114">
+      <c r="Q114">
         <v>1</v>
       </c>
       <c r="R114">
@@ -3416,13 +3341,13 @@
       <c r="A115" t="s">
         <v>133</v>
       </c>
-      <c r="D115">
-        <v>1</v>
-      </c>
-      <c r="E115">
-        <v>1</v>
-      </c>
-      <c r="F115">
+      <c r="R115">
+        <v>1</v>
+      </c>
+      <c r="S115">
+        <v>1</v>
+      </c>
+      <c r="T115">
         <v>1</v>
       </c>
     </row>
@@ -3430,19 +3355,13 @@
       <c r="A116" t="s">
         <v>134</v>
       </c>
-      <c r="B116">
-        <v>1</v>
-      </c>
-      <c r="C116">
-        <v>1</v>
-      </c>
-      <c r="D116">
-        <v>1</v>
-      </c>
-      <c r="O116">
-        <v>1</v>
-      </c>
-      <c r="Q116">
+      <c r="R116">
+        <v>1</v>
+      </c>
+      <c r="S116">
+        <v>1</v>
+      </c>
+      <c r="T116">
         <v>1</v>
       </c>
     </row>
@@ -3453,25 +3372,10 @@
       <c r="B117">
         <v>1</v>
       </c>
-      <c r="C117">
-        <v>1</v>
-      </c>
       <c r="D117">
         <v>1</v>
       </c>
       <c r="E117">
-        <v>1</v>
-      </c>
-      <c r="G117">
-        <v>1</v>
-      </c>
-      <c r="H117">
-        <v>1</v>
-      </c>
-      <c r="O117">
-        <v>1</v>
-      </c>
-      <c r="Q117">
         <v>1</v>
       </c>
     </row>
@@ -3482,22 +3386,7 @@
       <c r="B118">
         <v>1</v>
       </c>
-      <c r="C118">
-        <v>1</v>
-      </c>
       <c r="D118">
-        <v>1</v>
-      </c>
-      <c r="G118">
-        <v>1</v>
-      </c>
-      <c r="H118">
-        <v>1</v>
-      </c>
-      <c r="O118">
-        <v>1</v>
-      </c>
-      <c r="Q118">
         <v>1</v>
       </c>
     </row>
@@ -3505,10 +3394,10 @@
       <c r="A119" t="s">
         <v>137</v>
       </c>
-      <c r="E119">
-        <v>1</v>
-      </c>
-      <c r="G119">
+      <c r="H119">
+        <v>1</v>
+      </c>
+      <c r="L119">
         <v>1</v>
       </c>
       <c r="R119">
@@ -3522,22 +3411,16 @@
       <c r="A120" t="s">
         <v>138</v>
       </c>
+      <c r="B120">
+        <v>1</v>
+      </c>
+      <c r="D120">
+        <v>1</v>
+      </c>
+      <c r="G120">
+        <v>1</v>
+      </c>
       <c r="H120">
-        <v>1</v>
-      </c>
-      <c r="I120">
-        <v>1</v>
-      </c>
-      <c r="K120">
-        <v>1</v>
-      </c>
-      <c r="L120">
-        <v>1</v>
-      </c>
-      <c r="R120">
-        <v>1</v>
-      </c>
-      <c r="S120">
         <v>1</v>
       </c>
     </row>
@@ -3545,16 +3428,16 @@
       <c r="A121" t="s">
         <v>139</v>
       </c>
-      <c r="K121">
-        <v>1</v>
-      </c>
-      <c r="L121">
-        <v>1</v>
-      </c>
-      <c r="M121">
-        <v>1</v>
-      </c>
-      <c r="P121">
+      <c r="H121">
+        <v>1</v>
+      </c>
+      <c r="R121">
+        <v>1</v>
+      </c>
+      <c r="S121">
+        <v>1</v>
+      </c>
+      <c r="T121">
         <v>1</v>
       </c>
     </row>
@@ -3562,10 +3445,10 @@
       <c r="A122" t="s">
         <v>140</v>
       </c>
-      <c r="M122">
-        <v>1</v>
-      </c>
-      <c r="N122">
+      <c r="R122">
+        <v>1</v>
+      </c>
+      <c r="S122">
         <v>1</v>
       </c>
     </row>
@@ -3573,13 +3456,22 @@
       <c r="A123" t="s">
         <v>141</v>
       </c>
-      <c r="B123">
-        <v>1</v>
-      </c>
-      <c r="D123">
-        <v>1</v>
-      </c>
-      <c r="E123">
+      <c r="H123">
+        <v>1</v>
+      </c>
+      <c r="I123">
+        <v>1</v>
+      </c>
+      <c r="J123">
+        <v>1</v>
+      </c>
+      <c r="L123">
+        <v>1</v>
+      </c>
+      <c r="R123">
+        <v>1</v>
+      </c>
+      <c r="S123">
         <v>1</v>
       </c>
     </row>
@@ -3587,16 +3479,13 @@
       <c r="A124" t="s">
         <v>142</v>
       </c>
+      <c r="B124">
+        <v>1</v>
+      </c>
+      <c r="D124">
+        <v>1</v>
+      </c>
       <c r="E124">
-        <v>1</v>
-      </c>
-      <c r="G124">
-        <v>1</v>
-      </c>
-      <c r="H124">
-        <v>1</v>
-      </c>
-      <c r="I124">
         <v>1</v>
       </c>
     </row>
@@ -3604,13 +3493,16 @@
       <c r="A125" t="s">
         <v>143</v>
       </c>
-      <c r="Q125">
-        <v>1</v>
-      </c>
-      <c r="R125">
-        <v>1</v>
-      </c>
-      <c r="T125">
+      <c r="B125">
+        <v>1</v>
+      </c>
+      <c r="D125">
+        <v>1</v>
+      </c>
+      <c r="E125">
+        <v>1</v>
+      </c>
+      <c r="G125">
         <v>1</v>
       </c>
     </row>
@@ -3618,10 +3510,10 @@
       <c r="A126" t="s">
         <v>144</v>
       </c>
-      <c r="S126">
-        <v>1</v>
-      </c>
-      <c r="T126">
+      <c r="D126">
+        <v>1</v>
+      </c>
+      <c r="G126">
         <v>1</v>
       </c>
     </row>
@@ -3629,10 +3521,13 @@
       <c r="A127" t="s">
         <v>145</v>
       </c>
-      <c r="B127">
-        <v>1</v>
-      </c>
-      <c r="D127">
+      <c r="E127">
+        <v>1</v>
+      </c>
+      <c r="R127">
+        <v>1</v>
+      </c>
+      <c r="S127">
         <v>1</v>
       </c>
     </row>
@@ -3640,10 +3535,22 @@
       <c r="A128" t="s">
         <v>146</v>
       </c>
-      <c r="B128">
-        <v>1</v>
-      </c>
       <c r="D128">
+        <v>1</v>
+      </c>
+      <c r="E128">
+        <v>1</v>
+      </c>
+      <c r="H128">
+        <v>1</v>
+      </c>
+      <c r="I128">
+        <v>1</v>
+      </c>
+      <c r="J128">
+        <v>1</v>
+      </c>
+      <c r="S128">
         <v>1</v>
       </c>
     </row>
@@ -3651,10 +3558,16 @@
       <c r="A129" t="s">
         <v>147</v>
       </c>
-      <c r="H129">
-        <v>1</v>
-      </c>
-      <c r="I129">
+      <c r="B129">
+        <v>1</v>
+      </c>
+      <c r="D129">
+        <v>1</v>
+      </c>
+      <c r="G129">
+        <v>1</v>
+      </c>
+      <c r="R129">
         <v>1</v>
       </c>
     </row>
@@ -3662,7 +3575,10 @@
       <c r="A130" t="s">
         <v>148</v>
       </c>
-      <c r="F130">
+      <c r="M130">
+        <v>1</v>
+      </c>
+      <c r="P130">
         <v>1</v>
       </c>
     </row>
@@ -3670,16 +3586,25 @@
       <c r="A131" t="s">
         <v>149</v>
       </c>
-      <c r="B131">
-        <v>1</v>
-      </c>
-      <c r="D131">
-        <v>1</v>
-      </c>
-      <c r="E131">
+      <c r="C131">
         <v>1</v>
       </c>
       <c r="G131">
+        <v>1</v>
+      </c>
+      <c r="H131">
+        <v>1</v>
+      </c>
+      <c r="I131">
+        <v>1</v>
+      </c>
+      <c r="O131">
+        <v>1</v>
+      </c>
+      <c r="Q131">
+        <v>1</v>
+      </c>
+      <c r="R131">
         <v>1</v>
       </c>
     </row>
@@ -3687,13 +3612,25 @@
       <c r="A132" t="s">
         <v>150</v>
       </c>
+      <c r="C132">
+        <v>1</v>
+      </c>
+      <c r="G132">
+        <v>1</v>
+      </c>
+      <c r="H132">
+        <v>1</v>
+      </c>
+      <c r="I132">
+        <v>1</v>
+      </c>
+      <c r="O132">
+        <v>1</v>
+      </c>
       <c r="Q132">
         <v>1</v>
       </c>
       <c r="R132">
-        <v>1</v>
-      </c>
-      <c r="T132">
         <v>1</v>
       </c>
     </row>
@@ -3701,13 +3638,25 @@
       <c r="A133" t="s">
         <v>151</v>
       </c>
+      <c r="C133">
+        <v>1</v>
+      </c>
+      <c r="G133">
+        <v>1</v>
+      </c>
       <c r="H133">
         <v>1</v>
       </c>
       <c r="I133">
         <v>1</v>
       </c>
-      <c r="J133">
+      <c r="O133">
+        <v>1</v>
+      </c>
+      <c r="Q133">
+        <v>1</v>
+      </c>
+      <c r="R133">
         <v>1</v>
       </c>
     </row>
@@ -3715,10 +3664,25 @@
       <c r="A134" t="s">
         <v>152</v>
       </c>
-      <c r="M134">
-        <v>1</v>
-      </c>
-      <c r="P134">
+      <c r="D134">
+        <v>1</v>
+      </c>
+      <c r="E134">
+        <v>1</v>
+      </c>
+      <c r="G134">
+        <v>1</v>
+      </c>
+      <c r="H134">
+        <v>1</v>
+      </c>
+      <c r="I134">
+        <v>1</v>
+      </c>
+      <c r="R134">
+        <v>1</v>
+      </c>
+      <c r="S134">
         <v>1</v>
       </c>
     </row>
@@ -3726,16 +3690,10 @@
       <c r="A135" t="s">
         <v>153</v>
       </c>
-      <c r="G135">
-        <v>1</v>
-      </c>
-      <c r="H135">
-        <v>1</v>
-      </c>
-      <c r="I135">
-        <v>1</v>
-      </c>
-      <c r="Q135">
+      <c r="B135">
+        <v>1</v>
+      </c>
+      <c r="D135">
         <v>1</v>
       </c>
     </row>
@@ -3743,10 +3701,10 @@
       <c r="A136" t="s">
         <v>154</v>
       </c>
-      <c r="B136">
-        <v>1</v>
-      </c>
-      <c r="D136">
+      <c r="S136">
+        <v>1</v>
+      </c>
+      <c r="T136">
         <v>1</v>
       </c>
     </row>
@@ -3754,16 +3712,16 @@
       <c r="A137" t="s">
         <v>155</v>
       </c>
-      <c r="K137">
-        <v>1</v>
-      </c>
-      <c r="L137">
-        <v>1</v>
-      </c>
-      <c r="M137">
-        <v>1</v>
-      </c>
-      <c r="P137">
+      <c r="E137">
+        <v>1</v>
+      </c>
+      <c r="H137">
+        <v>1</v>
+      </c>
+      <c r="I137">
+        <v>1</v>
+      </c>
+      <c r="R137">
         <v>1</v>
       </c>
     </row>
@@ -3771,16 +3729,10 @@
       <c r="A138" t="s">
         <v>156</v>
       </c>
-      <c r="K138">
-        <v>1</v>
-      </c>
-      <c r="L138">
-        <v>1</v>
-      </c>
-      <c r="M138">
-        <v>1</v>
-      </c>
-      <c r="P138">
+      <c r="H138">
+        <v>1</v>
+      </c>
+      <c r="I138">
         <v>1</v>
       </c>
     </row>
@@ -3788,13 +3740,16 @@
       <c r="A139" t="s">
         <v>157</v>
       </c>
-      <c r="B139">
-        <v>1</v>
-      </c>
       <c r="D139">
         <v>1</v>
       </c>
       <c r="E139">
+        <v>1</v>
+      </c>
+      <c r="R139">
+        <v>1</v>
+      </c>
+      <c r="S139">
         <v>1</v>
       </c>
     </row>
@@ -3802,13 +3757,19 @@
       <c r="A140" t="s">
         <v>158</v>
       </c>
-      <c r="Q140">
-        <v>1</v>
-      </c>
-      <c r="R140">
-        <v>1</v>
-      </c>
-      <c r="T140">
+      <c r="D140">
+        <v>1</v>
+      </c>
+      <c r="G140">
+        <v>1</v>
+      </c>
+      <c r="H140">
+        <v>1</v>
+      </c>
+      <c r="I140">
+        <v>1</v>
+      </c>
+      <c r="S140">
         <v>1</v>
       </c>
     </row>
@@ -3816,16 +3777,19 @@
       <c r="A141" t="s">
         <v>159</v>
       </c>
-      <c r="G141">
-        <v>1</v>
-      </c>
-      <c r="R141">
+      <c r="E141">
+        <v>1</v>
+      </c>
+      <c r="F141">
+        <v>1</v>
+      </c>
+      <c r="H141">
+        <v>1</v>
+      </c>
+      <c r="I141">
         <v>1</v>
       </c>
       <c r="S141">
-        <v>1</v>
-      </c>
-      <c r="T141">
         <v>1</v>
       </c>
     </row>
@@ -3833,22 +3797,19 @@
       <c r="A142" t="s">
         <v>160</v>
       </c>
-      <c r="E142">
-        <v>1</v>
-      </c>
-      <c r="F142">
-        <v>1</v>
-      </c>
-      <c r="G142">
-        <v>1</v>
-      </c>
-      <c r="H142">
-        <v>1</v>
-      </c>
-      <c r="I142">
+      <c r="K142">
         <v>1</v>
       </c>
       <c r="L142">
+        <v>1</v>
+      </c>
+      <c r="M142">
+        <v>1</v>
+      </c>
+      <c r="P142">
+        <v>1</v>
+      </c>
+      <c r="S142">
         <v>1</v>
       </c>
     </row>
@@ -3856,10 +3817,22 @@
       <c r="A143" t="s">
         <v>161</v>
       </c>
-      <c r="B143">
+      <c r="D143">
+        <v>1</v>
+      </c>
+      <c r="E143">
+        <v>1</v>
+      </c>
+      <c r="G143">
+        <v>1</v>
+      </c>
+      <c r="H143">
         <v>1</v>
       </c>
       <c r="K143">
+        <v>1</v>
+      </c>
+      <c r="S143">
         <v>1</v>
       </c>
     </row>
@@ -3867,13 +3840,22 @@
       <c r="A144" t="s">
         <v>162</v>
       </c>
-      <c r="B144">
+      <c r="E144">
+        <v>1</v>
+      </c>
+      <c r="F144">
         <v>1</v>
       </c>
       <c r="G144">
         <v>1</v>
       </c>
       <c r="H144">
+        <v>1</v>
+      </c>
+      <c r="R144">
+        <v>1</v>
+      </c>
+      <c r="S144">
         <v>1</v>
       </c>
     </row>
@@ -3887,13 +3869,10 @@
       <c r="E145">
         <v>1</v>
       </c>
-      <c r="F145">
+      <c r="G145">
         <v>1</v>
       </c>
       <c r="R145">
-        <v>1</v>
-      </c>
-      <c r="S145">
         <v>1</v>
       </c>
     </row>
@@ -3901,10 +3880,10 @@
       <c r="A146" t="s">
         <v>164</v>
       </c>
+      <c r="H146">
+        <v>1</v>
+      </c>
       <c r="R146">
-        <v>1</v>
-      </c>
-      <c r="S146">
         <v>1</v>
       </c>
       <c r="T146">
@@ -3915,37 +3894,16 @@
       <c r="A147" t="s">
         <v>165</v>
       </c>
-      <c r="B147">
-        <v>1</v>
-      </c>
-      <c r="C147">
-        <v>1</v>
-      </c>
-      <c r="D147">
-        <v>1</v>
-      </c>
-      <c r="E147">
-        <v>1</v>
-      </c>
-      <c r="G147">
-        <v>1</v>
-      </c>
-      <c r="H147">
-        <v>1</v>
-      </c>
-      <c r="O147">
-        <v>1</v>
-      </c>
-      <c r="Q147">
-        <v>1</v>
-      </c>
-      <c r="R147">
-        <v>1</v>
-      </c>
-      <c r="S147">
-        <v>1</v>
-      </c>
-      <c r="T147">
+      <c r="K147">
+        <v>1</v>
+      </c>
+      <c r="L147">
+        <v>1</v>
+      </c>
+      <c r="M147">
+        <v>1</v>
+      </c>
+      <c r="P147">
         <v>1</v>
       </c>
     </row>
@@ -3953,16 +3911,16 @@
       <c r="A148" t="s">
         <v>166</v>
       </c>
-      <c r="E148">
-        <v>1</v>
-      </c>
       <c r="G148">
         <v>1</v>
       </c>
       <c r="H148">
         <v>1</v>
       </c>
-      <c r="O148">
+      <c r="I148">
+        <v>1</v>
+      </c>
+      <c r="R148">
         <v>1</v>
       </c>
     </row>
@@ -3970,19 +3928,16 @@
       <c r="A149" t="s">
         <v>167</v>
       </c>
-      <c r="C149">
-        <v>1</v>
-      </c>
-      <c r="D149">
-        <v>1</v>
-      </c>
       <c r="G149">
         <v>1</v>
       </c>
-      <c r="O149">
-        <v>1</v>
-      </c>
-      <c r="Q149">
+      <c r="H149">
+        <v>1</v>
+      </c>
+      <c r="I149">
+        <v>1</v>
+      </c>
+      <c r="R149">
         <v>1</v>
       </c>
     </row>
@@ -3990,19 +3945,13 @@
       <c r="A150" t="s">
         <v>168</v>
       </c>
-      <c r="C150">
-        <v>1</v>
-      </c>
-      <c r="D150">
-        <v>1</v>
-      </c>
       <c r="G150">
         <v>1</v>
       </c>
-      <c r="O150">
-        <v>1</v>
-      </c>
-      <c r="Q150">
+      <c r="H150">
+        <v>1</v>
+      </c>
+      <c r="I150">
         <v>1</v>
       </c>
       <c r="R150">
@@ -4013,16 +3962,22 @@
       <c r="A151" t="s">
         <v>169</v>
       </c>
-      <c r="Q151">
+      <c r="D151">
+        <v>1</v>
+      </c>
+      <c r="G151">
+        <v>1</v>
+      </c>
+      <c r="H151">
+        <v>1</v>
+      </c>
+      <c r="I151">
         <v>1</v>
       </c>
       <c r="R151">
         <v>1</v>
       </c>
       <c r="S151">
-        <v>1</v>
-      </c>
-      <c r="T151">
         <v>1</v>
       </c>
     </row>
@@ -4041,13 +3996,10 @@
       <c r="A153" t="s">
         <v>171</v>
       </c>
-      <c r="G153">
-        <v>1</v>
-      </c>
-      <c r="H153">
-        <v>1</v>
-      </c>
-      <c r="I153">
+      <c r="M153">
+        <v>1</v>
+      </c>
+      <c r="P153">
         <v>1</v>
       </c>
     </row>
@@ -4055,13 +4007,13 @@
       <c r="A154" t="s">
         <v>172</v>
       </c>
-      <c r="G154">
-        <v>1</v>
-      </c>
-      <c r="H154">
-        <v>1</v>
-      </c>
-      <c r="I154">
+      <c r="M154">
+        <v>1</v>
+      </c>
+      <c r="N154">
+        <v>1</v>
+      </c>
+      <c r="P154">
         <v>1</v>
       </c>
     </row>
@@ -4069,13 +4021,7 @@
       <c r="A155" t="s">
         <v>173</v>
       </c>
-      <c r="G155">
-        <v>1</v>
-      </c>
-      <c r="H155">
-        <v>1</v>
-      </c>
-      <c r="I155">
+      <c r="N155">
         <v>1</v>
       </c>
     </row>
@@ -4083,12 +4029,6 @@
       <c r="A156" t="s">
         <v>174</v>
       </c>
-      <c r="D156">
-        <v>1</v>
-      </c>
-      <c r="E156">
-        <v>1</v>
-      </c>
       <c r="G156">
         <v>1</v>
       </c>
@@ -4109,34 +4049,10 @@
       <c r="A157" t="s">
         <v>175</v>
       </c>
-      <c r="B157">
-        <v>1</v>
-      </c>
-      <c r="C157">
-        <v>1</v>
-      </c>
-      <c r="D157">
-        <v>1</v>
-      </c>
-      <c r="E157">
-        <v>1</v>
-      </c>
-      <c r="G157">
-        <v>1</v>
-      </c>
-      <c r="H157">
-        <v>1</v>
-      </c>
-      <c r="O157">
-        <v>1</v>
-      </c>
-      <c r="Q157">
-        <v>1</v>
-      </c>
-      <c r="R157">
-        <v>1</v>
-      </c>
-      <c r="T157">
+      <c r="M157">
+        <v>1</v>
+      </c>
+      <c r="P157">
         <v>1</v>
       </c>
     </row>
@@ -4144,22 +4060,13 @@
       <c r="A158" t="s">
         <v>176</v>
       </c>
-      <c r="C158">
-        <v>1</v>
-      </c>
-      <c r="K158">
-        <v>1</v>
-      </c>
-      <c r="M158">
-        <v>1</v>
-      </c>
-      <c r="O158">
-        <v>1</v>
-      </c>
-      <c r="P158">
-        <v>1</v>
-      </c>
-      <c r="Q158">
+      <c r="G158">
+        <v>1</v>
+      </c>
+      <c r="H158">
+        <v>1</v>
+      </c>
+      <c r="I158">
         <v>1</v>
       </c>
     </row>
@@ -4167,25 +4074,7 @@
       <c r="A159" t="s">
         <v>177</v>
       </c>
-      <c r="B159">
-        <v>1</v>
-      </c>
-      <c r="C159">
-        <v>1</v>
-      </c>
-      <c r="G159">
-        <v>1</v>
-      </c>
-      <c r="H159">
-        <v>1</v>
-      </c>
-      <c r="K159">
-        <v>1</v>
-      </c>
-      <c r="O159">
-        <v>1</v>
-      </c>
-      <c r="Q159">
+      <c r="N159">
         <v>1</v>
       </c>
     </row>
@@ -4196,19 +4085,13 @@
       <c r="B160">
         <v>1</v>
       </c>
-      <c r="C160">
-        <v>1</v>
-      </c>
-      <c r="D160">
-        <v>1</v>
-      </c>
       <c r="G160">
         <v>1</v>
       </c>
-      <c r="O160">
-        <v>1</v>
-      </c>
-      <c r="Q160">
+      <c r="H160">
+        <v>1</v>
+      </c>
+      <c r="I160">
         <v>1</v>
       </c>
     </row>
@@ -4216,16 +4099,10 @@
       <c r="A161" t="s">
         <v>179</v>
       </c>
-      <c r="E161">
-        <v>1</v>
-      </c>
-      <c r="G161">
-        <v>1</v>
-      </c>
-      <c r="H161">
-        <v>1</v>
-      </c>
-      <c r="S161">
+      <c r="M161">
+        <v>1</v>
+      </c>
+      <c r="P161">
         <v>1</v>
       </c>
     </row>
@@ -4233,25 +4110,16 @@
       <c r="A162" t="s">
         <v>180</v>
       </c>
-      <c r="B162">
-        <v>1</v>
-      </c>
-      <c r="C162">
-        <v>1</v>
-      </c>
-      <c r="D162">
-        <v>1</v>
-      </c>
-      <c r="G162">
-        <v>1</v>
-      </c>
       <c r="H162">
         <v>1</v>
       </c>
-      <c r="O162">
-        <v>1</v>
-      </c>
-      <c r="Q162">
+      <c r="I162">
+        <v>1</v>
+      </c>
+      <c r="K162">
+        <v>1</v>
+      </c>
+      <c r="L162">
         <v>1</v>
       </c>
     </row>
@@ -4259,25 +4127,22 @@
       <c r="A163" t="s">
         <v>181</v>
       </c>
-      <c r="B163">
-        <v>1</v>
-      </c>
-      <c r="C163">
-        <v>1</v>
-      </c>
       <c r="D163">
         <v>1</v>
       </c>
+      <c r="E163">
+        <v>1</v>
+      </c>
+      <c r="F163">
+        <v>1</v>
+      </c>
       <c r="G163">
         <v>1</v>
       </c>
-      <c r="O163">
-        <v>1</v>
-      </c>
-      <c r="Q163">
-        <v>1</v>
-      </c>
-      <c r="R163">
+      <c r="H163">
+        <v>1</v>
+      </c>
+      <c r="S163">
         <v>1</v>
       </c>
     </row>
@@ -4285,25 +4150,19 @@
       <c r="A164" t="s">
         <v>182</v>
       </c>
-      <c r="B164">
-        <v>1</v>
-      </c>
       <c r="D164">
         <v>1</v>
       </c>
-      <c r="E164">
-        <v>1</v>
-      </c>
-      <c r="G164">
-        <v>1</v>
-      </c>
-      <c r="H164">
-        <v>1</v>
-      </c>
-      <c r="I164">
-        <v>1</v>
-      </c>
-      <c r="R164">
+      <c r="K164">
+        <v>1</v>
+      </c>
+      <c r="L164">
+        <v>1</v>
+      </c>
+      <c r="P164">
+        <v>1</v>
+      </c>
+      <c r="S164">
         <v>1</v>
       </c>
     </row>
@@ -4311,28 +4170,13 @@
       <c r="A165" t="s">
         <v>183</v>
       </c>
-      <c r="B165">
-        <v>1</v>
-      </c>
-      <c r="C165">
-        <v>1</v>
-      </c>
-      <c r="D165">
-        <v>1</v>
-      </c>
-      <c r="G165">
-        <v>1</v>
-      </c>
-      <c r="H165">
-        <v>1</v>
-      </c>
-      <c r="O165">
-        <v>1</v>
-      </c>
-      <c r="Q165">
-        <v>1</v>
-      </c>
-      <c r="R165">
+      <c r="E165">
+        <v>1</v>
+      </c>
+      <c r="F165">
+        <v>1</v>
+      </c>
+      <c r="S165">
         <v>1</v>
       </c>
     </row>
@@ -4340,13 +4184,13 @@
       <c r="A166" t="s">
         <v>184</v>
       </c>
-      <c r="C166">
-        <v>1</v>
-      </c>
-      <c r="O166">
-        <v>1</v>
-      </c>
-      <c r="Q166">
+      <c r="G166">
+        <v>1</v>
+      </c>
+      <c r="H166">
+        <v>1</v>
+      </c>
+      <c r="I166">
         <v>1</v>
       </c>
     </row>
@@ -4354,13 +4198,10 @@
       <c r="A167" t="s">
         <v>185</v>
       </c>
-      <c r="C167">
-        <v>1</v>
-      </c>
-      <c r="O167">
-        <v>1</v>
-      </c>
-      <c r="Q167">
+      <c r="H167">
+        <v>1</v>
+      </c>
+      <c r="I167">
         <v>1</v>
       </c>
     </row>
@@ -4368,19 +4209,13 @@
       <c r="A168" t="s">
         <v>186</v>
       </c>
-      <c r="C168">
-        <v>1</v>
-      </c>
       <c r="G168">
         <v>1</v>
       </c>
-      <c r="O168">
-        <v>1</v>
-      </c>
-      <c r="Q168">
-        <v>1</v>
-      </c>
-      <c r="R168">
+      <c r="H168">
+        <v>1</v>
+      </c>
+      <c r="I168">
         <v>1</v>
       </c>
     </row>
@@ -4388,22 +4223,13 @@
       <c r="A169" t="s">
         <v>187</v>
       </c>
-      <c r="B169">
-        <v>1</v>
-      </c>
-      <c r="C169">
-        <v>1</v>
-      </c>
-      <c r="D169">
-        <v>1</v>
-      </c>
-      <c r="G169">
-        <v>1</v>
-      </c>
-      <c r="O169">
-        <v>1</v>
-      </c>
-      <c r="Q169">
+      <c r="J169">
+        <v>1</v>
+      </c>
+      <c r="S169">
+        <v>1</v>
+      </c>
+      <c r="T169">
         <v>1</v>
       </c>
     </row>
@@ -4411,19 +4237,22 @@
       <c r="A170" t="s">
         <v>188</v>
       </c>
-      <c r="D170">
-        <v>1</v>
-      </c>
-      <c r="E170">
-        <v>1</v>
-      </c>
-      <c r="G170">
-        <v>1</v>
-      </c>
       <c r="H170">
         <v>1</v>
       </c>
-      <c r="O170">
+      <c r="I170">
+        <v>1</v>
+      </c>
+      <c r="J170">
+        <v>1</v>
+      </c>
+      <c r="L170">
+        <v>1</v>
+      </c>
+      <c r="S170">
+        <v>1</v>
+      </c>
+      <c r="T170">
         <v>1</v>
       </c>
     </row>
@@ -4431,22 +4260,16 @@
       <c r="A171" t="s">
         <v>189</v>
       </c>
-      <c r="B171">
-        <v>1</v>
-      </c>
-      <c r="D171">
-        <v>1</v>
-      </c>
-      <c r="G171">
-        <v>1</v>
-      </c>
-      <c r="J171">
-        <v>1</v>
-      </c>
-      <c r="O171">
-        <v>1</v>
-      </c>
-      <c r="Q171">
+      <c r="L171">
+        <v>1</v>
+      </c>
+      <c r="R171">
+        <v>1</v>
+      </c>
+      <c r="S171">
+        <v>1</v>
+      </c>
+      <c r="T171">
         <v>1</v>
       </c>
     </row>
@@ -4454,22 +4277,13 @@
       <c r="A172" t="s">
         <v>190</v>
       </c>
-      <c r="B172">
-        <v>1</v>
-      </c>
-      <c r="C172">
-        <v>1</v>
-      </c>
-      <c r="D172">
-        <v>1</v>
-      </c>
-      <c r="G172">
-        <v>1</v>
-      </c>
-      <c r="O172">
-        <v>1</v>
-      </c>
-      <c r="Q172">
+      <c r="H172">
+        <v>1</v>
+      </c>
+      <c r="J172">
+        <v>1</v>
+      </c>
+      <c r="S172">
         <v>1</v>
       </c>
     </row>
@@ -4477,25 +4291,10 @@
       <c r="A173" t="s">
         <v>191</v>
       </c>
-      <c r="G173">
-        <v>1</v>
-      </c>
-      <c r="H173">
-        <v>1</v>
-      </c>
-      <c r="I173">
-        <v>1</v>
-      </c>
-      <c r="K173">
-        <v>1</v>
-      </c>
-      <c r="L173">
-        <v>1</v>
-      </c>
-      <c r="O173">
-        <v>1</v>
-      </c>
-      <c r="R173">
+      <c r="J173">
+        <v>1</v>
+      </c>
+      <c r="S173">
         <v>1</v>
       </c>
     </row>
@@ -4503,25 +4302,10 @@
       <c r="A174" t="s">
         <v>192</v>
       </c>
-      <c r="B174">
-        <v>1</v>
-      </c>
-      <c r="C174">
-        <v>1</v>
-      </c>
-      <c r="D174">
-        <v>1</v>
-      </c>
-      <c r="G174">
-        <v>1</v>
-      </c>
-      <c r="H174">
-        <v>1</v>
-      </c>
-      <c r="O174">
-        <v>1</v>
-      </c>
-      <c r="R174">
+      <c r="J174">
+        <v>1</v>
+      </c>
+      <c r="S174">
         <v>1</v>
       </c>
       <c r="T174">
@@ -4532,16 +4316,10 @@
       <c r="A175" t="s">
         <v>193</v>
       </c>
-      <c r="G175">
-        <v>1</v>
-      </c>
-      <c r="H175">
-        <v>1</v>
-      </c>
-      <c r="O175">
-        <v>1</v>
-      </c>
-      <c r="Q175">
+      <c r="J175">
+        <v>1</v>
+      </c>
+      <c r="S175">
         <v>1</v>
       </c>
     </row>
@@ -4549,258 +4327,264 @@
       <c r="A176" t="s">
         <v>194</v>
       </c>
-      <c r="M176">
-        <v>1</v>
-      </c>
-      <c r="N176">
-        <v>1</v>
-      </c>
-      <c r="P176">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="177" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="J176">
+        <v>1</v>
+      </c>
+      <c r="S176">
+        <v>1</v>
+      </c>
+      <c r="T176">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
         <v>195</v>
       </c>
-      <c r="N177">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="178" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="E177">
+        <v>1</v>
+      </c>
+      <c r="G177">
+        <v>1</v>
+      </c>
+      <c r="H177">
+        <v>1</v>
+      </c>
+      <c r="I177">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
         <v>196</v>
       </c>
-      <c r="R178">
-        <v>1</v>
-      </c>
-      <c r="S178">
-        <v>1</v>
-      </c>
-      <c r="T178">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="179" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="C178">
+        <v>1</v>
+      </c>
+      <c r="D178">
+        <v>1</v>
+      </c>
+      <c r="G178">
+        <v>1</v>
+      </c>
+      <c r="O178">
+        <v>1</v>
+      </c>
+      <c r="Q178">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
         <v>197</v>
       </c>
-      <c r="R179">
-        <v>1</v>
-      </c>
-      <c r="S179">
-        <v>1</v>
-      </c>
-      <c r="T179">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="180" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="C179">
+        <v>1</v>
+      </c>
+      <c r="D179">
+        <v>1</v>
+      </c>
+      <c r="G179">
+        <v>1</v>
+      </c>
+      <c r="O179">
+        <v>1</v>
+      </c>
+      <c r="Q179">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
         <v>198</v>
       </c>
+      <c r="B180">
+        <v>1</v>
+      </c>
+      <c r="D180">
+        <v>1</v>
+      </c>
       <c r="G180">
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
         <v>199</v>
       </c>
+      <c r="B181">
+        <v>1</v>
+      </c>
+      <c r="D181">
+        <v>1</v>
+      </c>
       <c r="G181">
         <v>1</v>
       </c>
-      <c r="J181">
-        <v>1</v>
-      </c>
-      <c r="K181">
-        <v>1</v>
-      </c>
-      <c r="P181">
-        <v>1</v>
-      </c>
-      <c r="S181">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="182" spans="1:20" x14ac:dyDescent="0.45">
+    </row>
+    <row r="182" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
         <v>200</v>
       </c>
       <c r="G182">
         <v>1</v>
       </c>
-      <c r="J182">
-        <v>1</v>
-      </c>
-      <c r="K182">
-        <v>1</v>
-      </c>
-      <c r="S182">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="183" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="H182">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
         <v>201</v>
       </c>
-      <c r="G183">
-        <v>1</v>
-      </c>
-      <c r="H183">
-        <v>1</v>
-      </c>
-      <c r="J183">
-        <v>1</v>
-      </c>
-      <c r="K183">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="184" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="C183">
+        <v>1</v>
+      </c>
+      <c r="E183">
+        <v>1</v>
+      </c>
+      <c r="O183">
+        <v>1</v>
+      </c>
+      <c r="Q183">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
         <v>202</v>
       </c>
-      <c r="G184">
-        <v>1</v>
-      </c>
-      <c r="H184">
-        <v>1</v>
-      </c>
-      <c r="I184">
+      <c r="C184">
+        <v>1</v>
+      </c>
+      <c r="D184">
+        <v>1</v>
+      </c>
+      <c r="E184">
+        <v>1</v>
+      </c>
+      <c r="F184">
+        <v>1</v>
+      </c>
+      <c r="O184">
+        <v>1</v>
+      </c>
+      <c r="Q184">
         <v>1</v>
       </c>
       <c r="R184">
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
         <v>203</v>
       </c>
-      <c r="G185">
-        <v>1</v>
-      </c>
-      <c r="H185">
-        <v>1</v>
-      </c>
-      <c r="I185">
-        <v>1</v>
-      </c>
-      <c r="J185">
-        <v>1</v>
-      </c>
-      <c r="R185">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="186" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="C185">
+        <v>1</v>
+      </c>
+      <c r="E185">
+        <v>1</v>
+      </c>
+      <c r="O185">
+        <v>1</v>
+      </c>
+      <c r="Q185">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
         <v>204</v>
       </c>
-      <c r="H186">
-        <v>1</v>
-      </c>
-      <c r="J186">
-        <v>1</v>
-      </c>
-      <c r="S186">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="187" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="C186">
+        <v>1</v>
+      </c>
+      <c r="E186">
+        <v>1</v>
+      </c>
+      <c r="O186">
+        <v>1</v>
+      </c>
+      <c r="Q186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
         <v>205</v>
       </c>
-      <c r="M187">
-        <v>1</v>
-      </c>
-      <c r="P187">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="188" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="C187">
+        <v>1</v>
+      </c>
+      <c r="E187">
+        <v>1</v>
+      </c>
+      <c r="O187">
+        <v>1</v>
+      </c>
+      <c r="Q187">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
         <v>206</v>
       </c>
-      <c r="K188">
-        <v>1</v>
-      </c>
-      <c r="L188">
-        <v>1</v>
-      </c>
-      <c r="M188">
-        <v>1</v>
-      </c>
-      <c r="P188">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="189" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="C188">
+        <v>1</v>
+      </c>
+      <c r="E188">
+        <v>1</v>
+      </c>
+      <c r="O188">
+        <v>1</v>
+      </c>
+      <c r="Q188">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A189" t="s">
         <v>207</v>
       </c>
-      <c r="S189">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="190" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="D189">
+        <v>1</v>
+      </c>
+      <c r="E189">
+        <v>1</v>
+      </c>
+      <c r="F189">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
         <v>208</v>
       </c>
-      <c r="G190">
-        <v>1</v>
-      </c>
-      <c r="H190">
-        <v>1</v>
-      </c>
-      <c r="K190">
-        <v>1</v>
-      </c>
-      <c r="L190">
-        <v>1</v>
-      </c>
-      <c r="M190">
-        <v>1</v>
-      </c>
-      <c r="P190">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="191" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="D190">
+        <v>1</v>
+      </c>
+      <c r="E190">
+        <v>1</v>
+      </c>
+      <c r="F190">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
         <v>209</v>
       </c>
-      <c r="D191">
-        <v>1</v>
-      </c>
-      <c r="G191">
-        <v>1</v>
-      </c>
-      <c r="H191">
-        <v>1</v>
-      </c>
-      <c r="K191">
-        <v>1</v>
-      </c>
-      <c r="P191">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="192" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="S191">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
         <v>210</v>
       </c>
-      <c r="B192">
-        <v>1</v>
-      </c>
-      <c r="D192">
-        <v>1</v>
-      </c>
-      <c r="E192">
-        <v>1</v>
-      </c>
-      <c r="R192">
+      <c r="F192">
         <v>1</v>
       </c>
     </row>
@@ -4808,13 +4592,19 @@
       <c r="A193" t="s">
         <v>211</v>
       </c>
-      <c r="G193">
-        <v>1</v>
-      </c>
-      <c r="H193">
-        <v>1</v>
-      </c>
-      <c r="I193">
+      <c r="B193">
+        <v>1</v>
+      </c>
+      <c r="C193">
+        <v>1</v>
+      </c>
+      <c r="D193">
+        <v>1</v>
+      </c>
+      <c r="O193">
+        <v>1</v>
+      </c>
+      <c r="Q193">
         <v>1</v>
       </c>
     </row>
@@ -4822,13 +4612,28 @@
       <c r="A194" t="s">
         <v>212</v>
       </c>
-      <c r="K194">
-        <v>1</v>
-      </c>
-      <c r="L194">
-        <v>1</v>
-      </c>
-      <c r="S194">
+      <c r="B194">
+        <v>1</v>
+      </c>
+      <c r="C194">
+        <v>1</v>
+      </c>
+      <c r="D194">
+        <v>1</v>
+      </c>
+      <c r="E194">
+        <v>1</v>
+      </c>
+      <c r="G194">
+        <v>1</v>
+      </c>
+      <c r="H194">
+        <v>1</v>
+      </c>
+      <c r="O194">
+        <v>1</v>
+      </c>
+      <c r="Q194">
         <v>1</v>
       </c>
     </row>
@@ -4836,25 +4641,25 @@
       <c r="A195" t="s">
         <v>213</v>
       </c>
+      <c r="B195">
+        <v>1</v>
+      </c>
+      <c r="C195">
+        <v>1</v>
+      </c>
       <c r="D195">
         <v>1</v>
       </c>
-      <c r="E195">
-        <v>1</v>
-      </c>
       <c r="G195">
         <v>1</v>
       </c>
       <c r="H195">
         <v>1</v>
       </c>
-      <c r="I195">
-        <v>1</v>
-      </c>
-      <c r="R195">
-        <v>1</v>
-      </c>
-      <c r="S195">
+      <c r="O195">
+        <v>1</v>
+      </c>
+      <c r="Q195">
         <v>1</v>
       </c>
     </row>
@@ -4862,10 +4667,22 @@
       <c r="A196" t="s">
         <v>214</v>
       </c>
-      <c r="B196">
-        <v>1</v>
-      </c>
-      <c r="D196">
+      <c r="H196">
+        <v>1</v>
+      </c>
+      <c r="I196">
+        <v>1</v>
+      </c>
+      <c r="K196">
+        <v>1</v>
+      </c>
+      <c r="L196">
+        <v>1</v>
+      </c>
+      <c r="R196">
+        <v>1</v>
+      </c>
+      <c r="S196">
         <v>1</v>
       </c>
     </row>
@@ -4873,6 +4690,33 @@
       <c r="A197" t="s">
         <v>215</v>
       </c>
+      <c r="B197">
+        <v>1</v>
+      </c>
+      <c r="C197">
+        <v>1</v>
+      </c>
+      <c r="D197">
+        <v>1</v>
+      </c>
+      <c r="E197">
+        <v>1</v>
+      </c>
+      <c r="G197">
+        <v>1</v>
+      </c>
+      <c r="H197">
+        <v>1</v>
+      </c>
+      <c r="O197">
+        <v>1</v>
+      </c>
+      <c r="Q197">
+        <v>1</v>
+      </c>
+      <c r="R197">
+        <v>1</v>
+      </c>
       <c r="S197">
         <v>1</v>
       </c>
@@ -4884,13 +4728,16 @@
       <c r="A198" t="s">
         <v>216</v>
       </c>
-      <c r="Q198">
-        <v>1</v>
-      </c>
-      <c r="R198">
-        <v>1</v>
-      </c>
-      <c r="T198">
+      <c r="E198">
+        <v>1</v>
+      </c>
+      <c r="G198">
+        <v>1</v>
+      </c>
+      <c r="H198">
+        <v>1</v>
+      </c>
+      <c r="O198">
         <v>1</v>
       </c>
     </row>
@@ -4898,13 +4745,19 @@
       <c r="A199" t="s">
         <v>217</v>
       </c>
+      <c r="C199">
+        <v>1</v>
+      </c>
+      <c r="D199">
+        <v>1</v>
+      </c>
       <c r="G199">
         <v>1</v>
       </c>
-      <c r="H199">
-        <v>1</v>
-      </c>
-      <c r="I199">
+      <c r="O199">
+        <v>1</v>
+      </c>
+      <c r="Q199">
         <v>1</v>
       </c>
     </row>
@@ -4912,10 +4765,19 @@
       <c r="A200" t="s">
         <v>218</v>
       </c>
-      <c r="E200">
-        <v>1</v>
-      </c>
-      <c r="F200">
+      <c r="C200">
+        <v>1</v>
+      </c>
+      <c r="D200">
+        <v>1</v>
+      </c>
+      <c r="G200">
+        <v>1</v>
+      </c>
+      <c r="O200">
+        <v>1</v>
+      </c>
+      <c r="Q200">
         <v>1</v>
       </c>
       <c r="R200">
@@ -4926,10 +4788,16 @@
       <c r="A201" t="s">
         <v>219</v>
       </c>
-      <c r="M201">
-        <v>1</v>
-      </c>
-      <c r="P201">
+      <c r="Q201">
+        <v>1</v>
+      </c>
+      <c r="R201">
+        <v>1</v>
+      </c>
+      <c r="S201">
+        <v>1</v>
+      </c>
+      <c r="T201">
         <v>1</v>
       </c>
     </row>
@@ -4937,13 +4805,10 @@
       <c r="A202" t="s">
         <v>220</v>
       </c>
-      <c r="G202">
-        <v>1</v>
-      </c>
       <c r="H202">
         <v>1</v>
       </c>
-      <c r="R202">
+      <c r="I202">
         <v>1</v>
       </c>
     </row>
@@ -4951,16 +4816,13 @@
       <c r="A203" t="s">
         <v>221</v>
       </c>
-      <c r="B203">
-        <v>1</v>
-      </c>
-      <c r="D203">
-        <v>1</v>
-      </c>
       <c r="G203">
         <v>1</v>
       </c>
       <c r="H203">
+        <v>1</v>
+      </c>
+      <c r="I203">
         <v>1</v>
       </c>
     </row>
@@ -4974,10 +4836,7 @@
       <c r="H204">
         <v>1</v>
       </c>
-      <c r="K204">
-        <v>1</v>
-      </c>
-      <c r="L204">
+      <c r="I204">
         <v>1</v>
       </c>
     </row>
@@ -4985,7 +4844,13 @@
       <c r="A205" t="s">
         <v>223</v>
       </c>
-      <c r="Q205">
+      <c r="G205">
+        <v>1</v>
+      </c>
+      <c r="H205">
+        <v>1</v>
+      </c>
+      <c r="I205">
         <v>1</v>
       </c>
     </row>
@@ -4993,10 +4858,25 @@
       <c r="A206" t="s">
         <v>224</v>
       </c>
-      <c r="S206">
-        <v>1</v>
-      </c>
-      <c r="T206">
+      <c r="D206">
+        <v>1</v>
+      </c>
+      <c r="E206">
+        <v>1</v>
+      </c>
+      <c r="G206">
+        <v>1</v>
+      </c>
+      <c r="H206">
+        <v>1</v>
+      </c>
+      <c r="I206">
+        <v>1</v>
+      </c>
+      <c r="J206">
+        <v>1</v>
+      </c>
+      <c r="R206">
         <v>1</v>
       </c>
     </row>
@@ -5004,13 +4884,31 @@
       <c r="A207" t="s">
         <v>225</v>
       </c>
+      <c r="B207">
+        <v>1</v>
+      </c>
+      <c r="C207">
+        <v>1</v>
+      </c>
+      <c r="D207">
+        <v>1</v>
+      </c>
+      <c r="E207">
+        <v>1</v>
+      </c>
+      <c r="G207">
+        <v>1</v>
+      </c>
+      <c r="H207">
+        <v>1</v>
+      </c>
+      <c r="O207">
+        <v>1</v>
+      </c>
       <c r="Q207">
         <v>1</v>
       </c>
       <c r="R207">
-        <v>1</v>
-      </c>
-      <c r="S207">
         <v>1</v>
       </c>
       <c r="T207">
@@ -5021,16 +4919,22 @@
       <c r="A208" t="s">
         <v>226</v>
       </c>
+      <c r="C208">
+        <v>1</v>
+      </c>
+      <c r="K208">
+        <v>1</v>
+      </c>
+      <c r="M208">
+        <v>1</v>
+      </c>
+      <c r="O208">
+        <v>1</v>
+      </c>
+      <c r="P208">
+        <v>1</v>
+      </c>
       <c r="Q208">
-        <v>1</v>
-      </c>
-      <c r="R208">
-        <v>1</v>
-      </c>
-      <c r="S208">
-        <v>1</v>
-      </c>
-      <c r="T208">
         <v>1</v>
       </c>
     </row>
@@ -5038,16 +4942,25 @@
       <c r="A209" t="s">
         <v>227</v>
       </c>
-      <c r="E209">
+      <c r="B209">
+        <v>1</v>
+      </c>
+      <c r="C209">
+        <v>1</v>
+      </c>
+      <c r="G209">
         <v>1</v>
       </c>
       <c r="H209">
         <v>1</v>
       </c>
-      <c r="I209">
-        <v>1</v>
-      </c>
-      <c r="R209">
+      <c r="K209">
+        <v>1</v>
+      </c>
+      <c r="O209">
+        <v>1</v>
+      </c>
+      <c r="Q209">
         <v>1</v>
       </c>
     </row>
@@ -5055,7 +4968,22 @@
       <c r="A210" t="s">
         <v>228</v>
       </c>
-      <c r="F210">
+      <c r="B210">
+        <v>1</v>
+      </c>
+      <c r="C210">
+        <v>1</v>
+      </c>
+      <c r="D210">
+        <v>1</v>
+      </c>
+      <c r="G210">
+        <v>1</v>
+      </c>
+      <c r="O210">
+        <v>1</v>
+      </c>
+      <c r="Q210">
         <v>1</v>
       </c>
     </row>
@@ -5063,7 +4991,7 @@
       <c r="A211" t="s">
         <v>229</v>
       </c>
-      <c r="B211">
+      <c r="E211">
         <v>1</v>
       </c>
       <c r="G211">
@@ -5072,7 +5000,7 @@
       <c r="H211">
         <v>1</v>
       </c>
-      <c r="K211">
+      <c r="S211">
         <v>1</v>
       </c>
     </row>
@@ -5080,7 +5008,25 @@
       <c r="A212" t="s">
         <v>230</v>
       </c>
-      <c r="S212">
+      <c r="B212">
+        <v>1</v>
+      </c>
+      <c r="C212">
+        <v>1</v>
+      </c>
+      <c r="D212">
+        <v>1</v>
+      </c>
+      <c r="G212">
+        <v>1</v>
+      </c>
+      <c r="H212">
+        <v>1</v>
+      </c>
+      <c r="O212">
+        <v>1</v>
+      </c>
+      <c r="Q212">
         <v>1</v>
       </c>
     </row>
@@ -5088,13 +5034,25 @@
       <c r="A213" t="s">
         <v>231</v>
       </c>
+      <c r="B213">
+        <v>1</v>
+      </c>
+      <c r="C213">
+        <v>1</v>
+      </c>
+      <c r="D213">
+        <v>1</v>
+      </c>
+      <c r="G213">
+        <v>1</v>
+      </c>
+      <c r="O213">
+        <v>1</v>
+      </c>
       <c r="Q213">
         <v>1</v>
       </c>
       <c r="R213">
-        <v>1</v>
-      </c>
-      <c r="T213">
         <v>1</v>
       </c>
     </row>
@@ -5102,13 +5060,25 @@
       <c r="A214" t="s">
         <v>232</v>
       </c>
+      <c r="B214">
+        <v>1</v>
+      </c>
+      <c r="D214">
+        <v>1</v>
+      </c>
+      <c r="E214">
+        <v>1</v>
+      </c>
+      <c r="G214">
+        <v>1</v>
+      </c>
+      <c r="H214">
+        <v>1</v>
+      </c>
+      <c r="I214">
+        <v>1</v>
+      </c>
       <c r="R214">
-        <v>1</v>
-      </c>
-      <c r="S214">
-        <v>1</v>
-      </c>
-      <c r="T214">
         <v>1</v>
       </c>
     </row>
@@ -5116,13 +5086,28 @@
       <c r="A215" t="s">
         <v>233</v>
       </c>
+      <c r="B215">
+        <v>1</v>
+      </c>
+      <c r="C215">
+        <v>1</v>
+      </c>
       <c r="D215">
         <v>1</v>
       </c>
-      <c r="E215">
-        <v>1</v>
-      </c>
       <c r="G215">
+        <v>1</v>
+      </c>
+      <c r="H215">
+        <v>1</v>
+      </c>
+      <c r="O215">
+        <v>1</v>
+      </c>
+      <c r="Q215">
+        <v>1</v>
+      </c>
+      <c r="R215">
         <v>1</v>
       </c>
     </row>
@@ -5130,7 +5115,13 @@
       <c r="A216" t="s">
         <v>234</v>
       </c>
-      <c r="P216">
+      <c r="C216">
+        <v>1</v>
+      </c>
+      <c r="O216">
+        <v>1</v>
+      </c>
+      <c r="Q216">
         <v>1</v>
       </c>
     </row>
@@ -5138,19 +5129,13 @@
       <c r="A217" t="s">
         <v>235</v>
       </c>
-      <c r="B217">
-        <v>1</v>
-      </c>
       <c r="C217">
         <v>1</v>
       </c>
-      <c r="D217">
-        <v>1</v>
-      </c>
-      <c r="G217">
-        <v>1</v>
-      </c>
       <c r="O217">
+        <v>1</v>
+      </c>
+      <c r="Q217">
         <v>1</v>
       </c>
     </row>
@@ -5158,13 +5143,19 @@
       <c r="A218" t="s">
         <v>236</v>
       </c>
+      <c r="C218">
+        <v>1</v>
+      </c>
+      <c r="G218">
+        <v>1</v>
+      </c>
+      <c r="O218">
+        <v>1</v>
+      </c>
+      <c r="Q218">
+        <v>1</v>
+      </c>
       <c r="R218">
-        <v>1</v>
-      </c>
-      <c r="S218">
-        <v>1</v>
-      </c>
-      <c r="T218">
         <v>1</v>
       </c>
     </row>
@@ -5175,10 +5166,19 @@
       <c r="B219">
         <v>1</v>
       </c>
+      <c r="C219">
+        <v>1</v>
+      </c>
       <c r="D219">
         <v>1</v>
       </c>
-      <c r="E219">
+      <c r="G219">
+        <v>1</v>
+      </c>
+      <c r="O219">
+        <v>1</v>
+      </c>
+      <c r="Q219">
         <v>1</v>
       </c>
     </row>
@@ -5186,10 +5186,19 @@
       <c r="A220" t="s">
         <v>238</v>
       </c>
-      <c r="B220">
-        <v>1</v>
-      </c>
       <c r="D220">
+        <v>1</v>
+      </c>
+      <c r="E220">
+        <v>1</v>
+      </c>
+      <c r="G220">
+        <v>1</v>
+      </c>
+      <c r="H220">
+        <v>1</v>
+      </c>
+      <c r="O220">
         <v>1</v>
       </c>
     </row>
@@ -5197,7 +5206,22 @@
       <c r="A221" t="s">
         <v>239</v>
       </c>
-      <c r="N221">
+      <c r="B221">
+        <v>1</v>
+      </c>
+      <c r="D221">
+        <v>1</v>
+      </c>
+      <c r="G221">
+        <v>1</v>
+      </c>
+      <c r="J221">
+        <v>1</v>
+      </c>
+      <c r="O221">
+        <v>1</v>
+      </c>
+      <c r="Q221">
         <v>1</v>
       </c>
     </row>
@@ -5205,13 +5229,22 @@
       <c r="A222" t="s">
         <v>240</v>
       </c>
-      <c r="R222">
-        <v>1</v>
-      </c>
-      <c r="S222">
-        <v>1</v>
-      </c>
-      <c r="T222">
+      <c r="B222">
+        <v>1</v>
+      </c>
+      <c r="C222">
+        <v>1</v>
+      </c>
+      <c r="D222">
+        <v>1</v>
+      </c>
+      <c r="G222">
+        <v>1</v>
+      </c>
+      <c r="O222">
+        <v>1</v>
+      </c>
+      <c r="Q222">
         <v>1</v>
       </c>
     </row>
@@ -5219,16 +5252,25 @@
       <c r="A223" t="s">
         <v>241</v>
       </c>
-      <c r="M223">
-        <v>1</v>
-      </c>
-      <c r="N223">
-        <v>1</v>
-      </c>
-      <c r="P223">
-        <v>1</v>
-      </c>
-      <c r="Q223">
+      <c r="G223">
+        <v>1</v>
+      </c>
+      <c r="H223">
+        <v>1</v>
+      </c>
+      <c r="I223">
+        <v>1</v>
+      </c>
+      <c r="K223">
+        <v>1</v>
+      </c>
+      <c r="L223">
+        <v>1</v>
+      </c>
+      <c r="O223">
+        <v>1</v>
+      </c>
+      <c r="R223">
         <v>1</v>
       </c>
     </row>
@@ -5236,10 +5278,28 @@
       <c r="A224" t="s">
         <v>242</v>
       </c>
-      <c r="J224">
-        <v>1</v>
-      </c>
-      <c r="S224">
+      <c r="B224">
+        <v>1</v>
+      </c>
+      <c r="C224">
+        <v>1</v>
+      </c>
+      <c r="D224">
+        <v>1</v>
+      </c>
+      <c r="G224">
+        <v>1</v>
+      </c>
+      <c r="H224">
+        <v>1</v>
+      </c>
+      <c r="O224">
+        <v>1</v>
+      </c>
+      <c r="R224">
+        <v>1</v>
+      </c>
+      <c r="T224">
         <v>1</v>
       </c>
     </row>
@@ -5247,13 +5307,16 @@
       <c r="A225" t="s">
         <v>243</v>
       </c>
-      <c r="R225">
-        <v>1</v>
-      </c>
-      <c r="S225">
-        <v>1</v>
-      </c>
-      <c r="T225">
+      <c r="G225">
+        <v>1</v>
+      </c>
+      <c r="H225">
+        <v>1</v>
+      </c>
+      <c r="O225">
+        <v>1</v>
+      </c>
+      <c r="Q225">
         <v>1</v>
       </c>
     </row>
@@ -5275,16 +5338,19 @@
       <c r="A227" t="s">
         <v>245</v>
       </c>
-      <c r="B227">
-        <v>1</v>
-      </c>
-      <c r="D227">
-        <v>1</v>
-      </c>
       <c r="G227">
         <v>1</v>
       </c>
-      <c r="H227">
+      <c r="J227">
+        <v>1</v>
+      </c>
+      <c r="K227">
+        <v>1</v>
+      </c>
+      <c r="P227">
+        <v>1</v>
+      </c>
+      <c r="S227">
         <v>1</v>
       </c>
     </row>
@@ -5292,13 +5358,13 @@
       <c r="A228" t="s">
         <v>246</v>
       </c>
-      <c r="H228">
-        <v>1</v>
-      </c>
-      <c r="L228">
-        <v>1</v>
-      </c>
-      <c r="R228">
+      <c r="G228">
+        <v>1</v>
+      </c>
+      <c r="J228">
+        <v>1</v>
+      </c>
+      <c r="K228">
         <v>1</v>
       </c>
       <c r="S228">
@@ -5309,16 +5375,16 @@
       <c r="A229" t="s">
         <v>247</v>
       </c>
-      <c r="B229">
-        <v>1</v>
-      </c>
-      <c r="D229">
-        <v>1</v>
-      </c>
       <c r="G229">
         <v>1</v>
       </c>
       <c r="H229">
+        <v>1</v>
+      </c>
+      <c r="J229">
+        <v>1</v>
+      </c>
+      <c r="K229">
         <v>1</v>
       </c>
     </row>
@@ -5326,25 +5392,13 @@
       <c r="A230" t="s">
         <v>248</v>
       </c>
-      <c r="B230">
-        <v>1</v>
-      </c>
-      <c r="C230">
-        <v>1</v>
-      </c>
-      <c r="D230">
-        <v>1</v>
-      </c>
-      <c r="E230">
-        <v>1</v>
-      </c>
       <c r="G230">
         <v>1</v>
       </c>
       <c r="H230">
         <v>1</v>
       </c>
-      <c r="K230">
+      <c r="I230">
         <v>1</v>
       </c>
     </row>
@@ -5352,13 +5406,19 @@
       <c r="A231" t="s">
         <v>249</v>
       </c>
-      <c r="B231">
-        <v>1</v>
-      </c>
-      <c r="D231">
+      <c r="E231">
         <v>1</v>
       </c>
       <c r="G231">
+        <v>1</v>
+      </c>
+      <c r="H231">
+        <v>1</v>
+      </c>
+      <c r="I231">
+        <v>1</v>
+      </c>
+      <c r="R231">
         <v>1</v>
       </c>
     </row>
@@ -5375,21 +5435,27 @@
       <c r="G232">
         <v>1</v>
       </c>
-      <c r="H232">
-        <v>1</v>
-      </c>
     </row>
     <row r="233" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A233" t="s">
         <v>251</v>
       </c>
-      <c r="K233">
-        <v>1</v>
-      </c>
-      <c r="L233">
-        <v>1</v>
-      </c>
-      <c r="P233">
+      <c r="B233">
+        <v>1</v>
+      </c>
+      <c r="C233">
+        <v>1</v>
+      </c>
+      <c r="D233">
+        <v>1</v>
+      </c>
+      <c r="G233">
+        <v>1</v>
+      </c>
+      <c r="H233">
+        <v>1</v>
+      </c>
+      <c r="O233">
         <v>1</v>
       </c>
     </row>
@@ -5397,16 +5463,10 @@
       <c r="A234" t="s">
         <v>252</v>
       </c>
-      <c r="B234">
-        <v>1</v>
-      </c>
-      <c r="D234">
-        <v>1</v>
-      </c>
-      <c r="G234">
-        <v>1</v>
-      </c>
-      <c r="H234">
+      <c r="S234">
+        <v>1</v>
+      </c>
+      <c r="T234">
         <v>1</v>
       </c>
     </row>
@@ -5414,13 +5474,13 @@
       <c r="A235" t="s">
         <v>253</v>
       </c>
-      <c r="K235">
-        <v>1</v>
-      </c>
-      <c r="L235">
-        <v>1</v>
-      </c>
-      <c r="P235">
+      <c r="R235">
+        <v>1</v>
+      </c>
+      <c r="S235">
+        <v>1</v>
+      </c>
+      <c r="T235">
         <v>1</v>
       </c>
     </row>
@@ -5428,16 +5488,13 @@
       <c r="A236" t="s">
         <v>254</v>
       </c>
-      <c r="D236">
-        <v>1</v>
-      </c>
-      <c r="E236">
-        <v>1</v>
-      </c>
-      <c r="G236">
-        <v>1</v>
-      </c>
-      <c r="H236">
+      <c r="R236">
+        <v>1</v>
+      </c>
+      <c r="S236">
+        <v>1</v>
+      </c>
+      <c r="T236">
         <v>1</v>
       </c>
     </row>
@@ -5445,19 +5502,19 @@
       <c r="A237" t="s">
         <v>255</v>
       </c>
-      <c r="D237">
-        <v>1</v>
-      </c>
-      <c r="G237">
-        <v>1</v>
-      </c>
-      <c r="H237">
-        <v>1</v>
-      </c>
-      <c r="I237">
-        <v>1</v>
-      </c>
-      <c r="J237">
+      <c r="K237">
+        <v>1</v>
+      </c>
+      <c r="L237">
+        <v>1</v>
+      </c>
+      <c r="P237">
+        <v>1</v>
+      </c>
+      <c r="S237">
+        <v>1</v>
+      </c>
+      <c r="T237">
         <v>1</v>
       </c>
     </row>
@@ -5465,13 +5522,13 @@
       <c r="A238" t="s">
         <v>256</v>
       </c>
-      <c r="B238">
-        <v>1</v>
-      </c>
-      <c r="D238">
-        <v>1</v>
-      </c>
-      <c r="E238">
+      <c r="R238">
+        <v>1</v>
+      </c>
+      <c r="S238">
+        <v>1</v>
+      </c>
+      <c r="T238">
         <v>1</v>
       </c>
     </row>
@@ -5479,16 +5536,13 @@
       <c r="A239" t="s">
         <v>257</v>
       </c>
-      <c r="E239">
-        <v>1</v>
-      </c>
-      <c r="G239">
-        <v>1</v>
-      </c>
-      <c r="H239">
-        <v>1</v>
-      </c>
-      <c r="I239">
+      <c r="R239">
+        <v>1</v>
+      </c>
+      <c r="S239">
+        <v>1</v>
+      </c>
+      <c r="T239">
         <v>1</v>
       </c>
     </row>
@@ -5496,16 +5550,13 @@
       <c r="A240" t="s">
         <v>258</v>
       </c>
-      <c r="D240">
-        <v>1</v>
-      </c>
-      <c r="E240">
-        <v>1</v>
-      </c>
-      <c r="G240">
-        <v>1</v>
-      </c>
-      <c r="H240">
+      <c r="K240">
+        <v>1</v>
+      </c>
+      <c r="L240">
+        <v>1</v>
+      </c>
+      <c r="S240">
         <v>1</v>
       </c>
     </row>
@@ -5513,19 +5564,13 @@
       <c r="A241" t="s">
         <v>259</v>
       </c>
-      <c r="D241">
-        <v>1</v>
-      </c>
-      <c r="G241">
-        <v>1</v>
-      </c>
-      <c r="H241">
-        <v>1</v>
-      </c>
-      <c r="I241">
-        <v>1</v>
-      </c>
-      <c r="J241">
+      <c r="Q241">
+        <v>1</v>
+      </c>
+      <c r="R241">
+        <v>1</v>
+      </c>
+      <c r="T241">
         <v>1</v>
       </c>
     </row>
@@ -5536,13 +5581,7 @@
       <c r="H242">
         <v>1</v>
       </c>
-      <c r="R242">
-        <v>1</v>
-      </c>
-      <c r="S242">
-        <v>1</v>
-      </c>
-      <c r="T242">
+      <c r="I242">
         <v>1</v>
       </c>
     </row>
@@ -5550,10 +5589,7 @@
       <c r="A243" t="s">
         <v>261</v>
       </c>
-      <c r="R243">
-        <v>1</v>
-      </c>
-      <c r="S243">
+      <c r="I243">
         <v>1</v>
       </c>
     </row>
@@ -5561,16 +5597,13 @@
       <c r="A244" t="s">
         <v>262</v>
       </c>
-      <c r="H244">
-        <v>1</v>
-      </c>
-      <c r="I244">
-        <v>1</v>
-      </c>
-      <c r="J244">
+      <c r="K244">
         <v>1</v>
       </c>
       <c r="L244">
+        <v>1</v>
+      </c>
+      <c r="P244">
         <v>1</v>
       </c>
       <c r="R244">
@@ -5584,13 +5617,13 @@
       <c r="A245" t="s">
         <v>263</v>
       </c>
-      <c r="B245">
-        <v>1</v>
-      </c>
-      <c r="D245">
-        <v>1</v>
-      </c>
-      <c r="E245">
+      <c r="C245">
+        <v>1</v>
+      </c>
+      <c r="Q245">
+        <v>1</v>
+      </c>
+      <c r="R245">
         <v>1</v>
       </c>
     </row>
@@ -5598,16 +5631,13 @@
       <c r="A246" t="s">
         <v>264</v>
       </c>
-      <c r="B246">
-        <v>1</v>
-      </c>
-      <c r="D246">
-        <v>1</v>
-      </c>
-      <c r="E246">
-        <v>1</v>
-      </c>
-      <c r="G246">
+      <c r="R246">
+        <v>1</v>
+      </c>
+      <c r="S246">
+        <v>1</v>
+      </c>
+      <c r="T246">
         <v>1</v>
       </c>
     </row>
@@ -5615,10 +5645,16 @@
       <c r="A247" t="s">
         <v>265</v>
       </c>
-      <c r="D247">
-        <v>1</v>
-      </c>
-      <c r="G247">
+      <c r="C247">
+        <v>1</v>
+      </c>
+      <c r="O247">
+        <v>1</v>
+      </c>
+      <c r="R247">
+        <v>1</v>
+      </c>
+      <c r="T247">
         <v>1</v>
       </c>
     </row>
@@ -5629,10 +5665,16 @@
       <c r="E248">
         <v>1</v>
       </c>
-      <c r="R248">
-        <v>1</v>
-      </c>
-      <c r="S248">
+      <c r="F248">
+        <v>1</v>
+      </c>
+      <c r="H248">
+        <v>1</v>
+      </c>
+      <c r="I248">
+        <v>1</v>
+      </c>
+      <c r="L248">
         <v>1</v>
       </c>
     </row>
@@ -5640,22 +5682,16 @@
       <c r="A249" t="s">
         <v>267</v>
       </c>
-      <c r="D249">
-        <v>1</v>
-      </c>
       <c r="E249">
         <v>1</v>
       </c>
+      <c r="F249">
+        <v>1</v>
+      </c>
+      <c r="G249">
+        <v>1</v>
+      </c>
       <c r="H249">
-        <v>1</v>
-      </c>
-      <c r="I249">
-        <v>1</v>
-      </c>
-      <c r="J249">
-        <v>1</v>
-      </c>
-      <c r="S249">
         <v>1</v>
       </c>
     </row>
@@ -5666,13 +5702,16 @@
       <c r="B250">
         <v>1</v>
       </c>
+      <c r="C250">
+        <v>1</v>
+      </c>
+      <c r="D250">
+        <v>1</v>
+      </c>
       <c r="G250">
         <v>1</v>
       </c>
       <c r="H250">
-        <v>1</v>
-      </c>
-      <c r="I250">
         <v>1</v>
       </c>
     </row>
@@ -5683,18 +5722,12 @@
       <c r="M251">
         <v>1</v>
       </c>
-      <c r="P251">
-        <v>1</v>
-      </c>
     </row>
     <row r="252" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A252" t="s">
         <v>270</v>
       </c>
-      <c r="C252">
-        <v>1</v>
-      </c>
-      <c r="O252">
+      <c r="Q252">
         <v>1</v>
       </c>
       <c r="R252">
@@ -5708,10 +5741,13 @@
       <c r="A253" t="s">
         <v>271</v>
       </c>
-      <c r="M253">
-        <v>1</v>
-      </c>
-      <c r="P253">
+      <c r="Q253">
+        <v>1</v>
+      </c>
+      <c r="R253">
+        <v>1</v>
+      </c>
+      <c r="T253">
         <v>1</v>
       </c>
     </row>
@@ -5719,16 +5755,13 @@
       <c r="A254" t="s">
         <v>272</v>
       </c>
-      <c r="H254">
-        <v>1</v>
-      </c>
-      <c r="I254">
-        <v>1</v>
-      </c>
-      <c r="K254">
-        <v>1</v>
-      </c>
-      <c r="L254">
+      <c r="Q254">
+        <v>1</v>
+      </c>
+      <c r="R254">
+        <v>1</v>
+      </c>
+      <c r="T254">
         <v>1</v>
       </c>
     </row>
@@ -5736,13 +5769,13 @@
       <c r="A255" t="s">
         <v>273</v>
       </c>
-      <c r="G255">
-        <v>1</v>
-      </c>
-      <c r="H255">
-        <v>1</v>
-      </c>
-      <c r="I255">
+      <c r="Q255">
+        <v>1</v>
+      </c>
+      <c r="R255">
+        <v>1</v>
+      </c>
+      <c r="T255">
         <v>1</v>
       </c>
     </row>
@@ -5750,13 +5783,13 @@
       <c r="A256" t="s">
         <v>274</v>
       </c>
-      <c r="H256">
-        <v>1</v>
-      </c>
-      <c r="I256">
-        <v>1</v>
-      </c>
-      <c r="J256">
+      <c r="Q256">
+        <v>1</v>
+      </c>
+      <c r="R256">
+        <v>1</v>
+      </c>
+      <c r="T256">
         <v>1</v>
       </c>
     </row>
@@ -5764,13 +5797,7 @@
       <c r="A257" t="s">
         <v>275</v>
       </c>
-      <c r="D257">
-        <v>1</v>
-      </c>
-      <c r="E257">
-        <v>1</v>
-      </c>
-      <c r="F257">
+      <c r="B257">
         <v>1</v>
       </c>
       <c r="G257">
@@ -5779,7 +5806,7 @@
       <c r="H257">
         <v>1</v>
       </c>
-      <c r="S257">
+      <c r="K257">
         <v>1</v>
       </c>
     </row>
@@ -5787,18 +5814,6 @@
       <c r="A258" t="s">
         <v>276</v>
       </c>
-      <c r="D258">
-        <v>1</v>
-      </c>
-      <c r="K258">
-        <v>1</v>
-      </c>
-      <c r="L258">
-        <v>1</v>
-      </c>
-      <c r="P258">
-        <v>1</v>
-      </c>
       <c r="S258">
         <v>1</v>
       </c>
@@ -5807,13 +5822,13 @@
       <c r="A259" t="s">
         <v>277</v>
       </c>
-      <c r="E259">
-        <v>1</v>
-      </c>
-      <c r="F259">
-        <v>1</v>
-      </c>
-      <c r="S259">
+      <c r="Q259">
+        <v>1</v>
+      </c>
+      <c r="R259">
+        <v>1</v>
+      </c>
+      <c r="T259">
         <v>1</v>
       </c>
     </row>
@@ -5821,10 +5836,19 @@
       <c r="A260" t="s">
         <v>278</v>
       </c>
-      <c r="S260">
-        <v>1</v>
-      </c>
-      <c r="T260">
+      <c r="B260">
+        <v>1</v>
+      </c>
+      <c r="C260">
+        <v>1</v>
+      </c>
+      <c r="D260">
+        <v>1</v>
+      </c>
+      <c r="G260">
+        <v>1</v>
+      </c>
+      <c r="O260">
         <v>1</v>
       </c>
     </row>
@@ -5832,7 +5856,16 @@
       <c r="A261" t="s">
         <v>279</v>
       </c>
+      <c r="M261">
+        <v>1</v>
+      </c>
       <c r="N261">
+        <v>1</v>
+      </c>
+      <c r="P261">
+        <v>1</v>
+      </c>
+      <c r="Q261">
         <v>1</v>
       </c>
     </row>
@@ -5840,10 +5873,13 @@
       <c r="A262" t="s">
         <v>280</v>
       </c>
-      <c r="M262">
-        <v>1</v>
-      </c>
-      <c r="P262">
+      <c r="G262">
+        <v>1</v>
+      </c>
+      <c r="H262">
+        <v>1</v>
+      </c>
+      <c r="I262">
         <v>1</v>
       </c>
     </row>
@@ -5851,16 +5887,13 @@
       <c r="A263" t="s">
         <v>281</v>
       </c>
-      <c r="K263">
-        <v>1</v>
-      </c>
-      <c r="L263">
-        <v>1</v>
-      </c>
-      <c r="M263">
-        <v>1</v>
-      </c>
-      <c r="P263">
+      <c r="H263">
+        <v>1</v>
+      </c>
+      <c r="I263">
+        <v>1</v>
+      </c>
+      <c r="J263">
         <v>1</v>
       </c>
     </row>
@@ -5868,10 +5901,10 @@
       <c r="A264" t="s">
         <v>282</v>
       </c>
-      <c r="H264">
-        <v>1</v>
-      </c>
-      <c r="I264">
+      <c r="S264">
+        <v>1</v>
+      </c>
+      <c r="T264">
         <v>1</v>
       </c>
     </row>
@@ -5888,24 +5921,18 @@
       <c r="D265">
         <v>1</v>
       </c>
-      <c r="G265">
-        <v>1</v>
-      </c>
-      <c r="K265">
-        <v>1</v>
-      </c>
-      <c r="R265">
-        <v>1</v>
-      </c>
     </row>
     <row r="266" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A266" t="s">
         <v>284</v>
       </c>
-      <c r="J266">
-        <v>1</v>
-      </c>
-      <c r="S266">
+      <c r="P266">
+        <v>1</v>
+      </c>
+      <c r="Q266">
+        <v>1</v>
+      </c>
+      <c r="R266">
         <v>1</v>
       </c>
       <c r="T266">
@@ -5916,13 +5943,13 @@
       <c r="A267" t="s">
         <v>285</v>
       </c>
-      <c r="G267">
-        <v>1</v>
-      </c>
-      <c r="H267">
-        <v>1</v>
-      </c>
-      <c r="I267">
+      <c r="C267">
+        <v>1</v>
+      </c>
+      <c r="Q267">
+        <v>1</v>
+      </c>
+      <c r="R267">
         <v>1</v>
       </c>
     </row>
@@ -5930,28 +5957,7 @@
       <c r="A268" t="s">
         <v>286</v>
       </c>
-      <c r="B268">
-        <v>1</v>
-      </c>
-      <c r="D268">
-        <v>1</v>
-      </c>
-      <c r="G268">
-        <v>1</v>
-      </c>
-      <c r="H268">
-        <v>1</v>
-      </c>
-      <c r="K268">
-        <v>1</v>
-      </c>
-      <c r="R268">
-        <v>1</v>
-      </c>
-      <c r="S268">
-        <v>1</v>
-      </c>
-      <c r="T268">
+      <c r="F268">
         <v>1</v>
       </c>
     </row>
@@ -5959,13 +5965,13 @@
       <c r="A269" t="s">
         <v>287</v>
       </c>
-      <c r="K269">
-        <v>1</v>
-      </c>
-      <c r="L269">
-        <v>1</v>
-      </c>
-      <c r="R269">
+      <c r="E269">
+        <v>1</v>
+      </c>
+      <c r="F269">
+        <v>1</v>
+      </c>
+      <c r="S269">
         <v>1</v>
       </c>
     </row>
@@ -5973,31 +5979,13 @@
       <c r="A270" t="s">
         <v>288</v>
       </c>
-      <c r="D270">
-        <v>1</v>
-      </c>
-      <c r="G270">
-        <v>1</v>
-      </c>
-      <c r="H270">
-        <v>1</v>
-      </c>
-      <c r="I270">
-        <v>1</v>
-      </c>
-      <c r="K270">
-        <v>1</v>
-      </c>
-      <c r="L270">
+      <c r="F270">
         <v>1</v>
       </c>
       <c r="R270">
         <v>1</v>
       </c>
       <c r="S270">
-        <v>1</v>
-      </c>
-      <c r="T270">
         <v>1</v>
       </c>
     </row>
@@ -6005,7 +5993,7 @@
       <c r="A271" t="s">
         <v>289</v>
       </c>
-      <c r="N271">
+      <c r="F271">
         <v>1</v>
       </c>
     </row>
@@ -6013,13 +6001,13 @@
       <c r="A272" t="s">
         <v>290</v>
       </c>
-      <c r="B272">
-        <v>1</v>
-      </c>
-      <c r="C272">
-        <v>1</v>
-      </c>
-      <c r="D272">
+      <c r="M272">
+        <v>1</v>
+      </c>
+      <c r="N272">
+        <v>1</v>
+      </c>
+      <c r="P272">
         <v>1</v>
       </c>
     </row>
@@ -6027,16 +6015,16 @@
       <c r="A273" t="s">
         <v>291</v>
       </c>
-      <c r="B273">
-        <v>1</v>
-      </c>
-      <c r="D273">
-        <v>1</v>
-      </c>
-      <c r="G273">
+      <c r="H273">
+        <v>1</v>
+      </c>
+      <c r="I273">
         <v>1</v>
       </c>
       <c r="R273">
+        <v>1</v>
+      </c>
+      <c r="S273">
         <v>1</v>
       </c>
     </row>
@@ -6044,13 +6032,10 @@
       <c r="A274" t="s">
         <v>292</v>
       </c>
-      <c r="M274">
-        <v>1</v>
-      </c>
-      <c r="N274">
-        <v>1</v>
-      </c>
-      <c r="P274">
+      <c r="R274">
+        <v>1</v>
+      </c>
+      <c r="T274">
         <v>1</v>
       </c>
     </row>
@@ -6058,10 +6043,16 @@
       <c r="A275" t="s">
         <v>293</v>
       </c>
-      <c r="M275">
-        <v>1</v>
-      </c>
-      <c r="P275">
+      <c r="C275">
+        <v>1</v>
+      </c>
+      <c r="D275">
+        <v>1</v>
+      </c>
+      <c r="O275">
+        <v>1</v>
+      </c>
+      <c r="R275">
         <v>1</v>
       </c>
     </row>
@@ -6069,7 +6060,7 @@
       <c r="A276" t="s">
         <v>294</v>
       </c>
-      <c r="P276">
+      <c r="O276">
         <v>1</v>
       </c>
       <c r="Q276">
@@ -6086,13 +6077,10 @@
       <c r="A277" t="s">
         <v>295</v>
       </c>
-      <c r="Q277">
-        <v>1</v>
-      </c>
-      <c r="R277">
-        <v>1</v>
-      </c>
-      <c r="T277">
+      <c r="K277">
+        <v>1</v>
+      </c>
+      <c r="L277">
         <v>1</v>
       </c>
     </row>
@@ -6100,16 +6088,10 @@
       <c r="A278" t="s">
         <v>296</v>
       </c>
-      <c r="B278">
-        <v>1</v>
-      </c>
-      <c r="D278">
-        <v>1</v>
-      </c>
-      <c r="G278">
-        <v>1</v>
-      </c>
-      <c r="H278">
+      <c r="R278">
+        <v>1</v>
+      </c>
+      <c r="T278">
         <v>1</v>
       </c>
     </row>
@@ -6120,7 +6102,13 @@
       <c r="C279">
         <v>1</v>
       </c>
-      <c r="Q279">
+      <c r="D279">
+        <v>1</v>
+      </c>
+      <c r="G279">
+        <v>1</v>
+      </c>
+      <c r="O279">
         <v>1</v>
       </c>
       <c r="R279">
@@ -6131,19 +6119,13 @@
       <c r="A280" t="s">
         <v>298</v>
       </c>
-      <c r="E280">
-        <v>1</v>
-      </c>
-      <c r="F280">
+      <c r="G280">
         <v>1</v>
       </c>
       <c r="H280">
         <v>1</v>
       </c>
       <c r="I280">
-        <v>1</v>
-      </c>
-      <c r="L280">
         <v>1</v>
       </c>
     </row>
@@ -6151,16 +6133,13 @@
       <c r="A281" t="s">
         <v>299</v>
       </c>
-      <c r="E281">
-        <v>1</v>
-      </c>
-      <c r="F281">
-        <v>1</v>
-      </c>
-      <c r="G281">
-        <v>1</v>
-      </c>
-      <c r="H281">
+      <c r="Q281">
+        <v>1</v>
+      </c>
+      <c r="R281">
+        <v>1</v>
+      </c>
+      <c r="T281">
         <v>1</v>
       </c>
     </row>
@@ -6168,19 +6147,13 @@
       <c r="A282" t="s">
         <v>300</v>
       </c>
-      <c r="B282">
-        <v>1</v>
-      </c>
-      <c r="C282">
-        <v>1</v>
-      </c>
-      <c r="D282">
-        <v>1</v>
-      </c>
-      <c r="G282">
-        <v>1</v>
-      </c>
-      <c r="H282">
+      <c r="Q282">
+        <v>1</v>
+      </c>
+      <c r="R282">
+        <v>1</v>
+      </c>
+      <c r="T282">
         <v>1</v>
       </c>
     </row>
@@ -6188,7 +6161,16 @@
       <c r="A283" t="s">
         <v>301</v>
       </c>
-      <c r="N283">
+      <c r="G283">
+        <v>1</v>
+      </c>
+      <c r="H283">
+        <v>1</v>
+      </c>
+      <c r="Q283">
+        <v>1</v>
+      </c>
+      <c r="R283">
         <v>1</v>
       </c>
     </row>
@@ -6196,7 +6178,13 @@
       <c r="A284" t="s">
         <v>302</v>
       </c>
-      <c r="N284">
+      <c r="Q284">
+        <v>1</v>
+      </c>
+      <c r="R284">
+        <v>1</v>
+      </c>
+      <c r="T284">
         <v>1</v>
       </c>
     </row>
@@ -6204,10 +6192,13 @@
       <c r="A285" t="s">
         <v>303</v>
       </c>
-      <c r="J285">
-        <v>1</v>
-      </c>
-      <c r="S285">
+      <c r="Q285">
+        <v>1</v>
+      </c>
+      <c r="R285">
+        <v>1</v>
+      </c>
+      <c r="T285">
         <v>1</v>
       </c>
     </row>
@@ -6215,13 +6206,13 @@
       <c r="A286" t="s">
         <v>304</v>
       </c>
-      <c r="G286">
-        <v>1</v>
-      </c>
-      <c r="H286">
-        <v>1</v>
-      </c>
-      <c r="I286">
+      <c r="Q286">
+        <v>1</v>
+      </c>
+      <c r="R286">
+        <v>1</v>
+      </c>
+      <c r="T286">
         <v>1</v>
       </c>
     </row>
@@ -6229,10 +6220,16 @@
       <c r="A287" t="s">
         <v>305</v>
       </c>
+      <c r="G287">
+        <v>1</v>
+      </c>
       <c r="H287">
         <v>1</v>
       </c>
       <c r="I287">
+        <v>1</v>
+      </c>
+      <c r="Q287">
         <v>1</v>
       </c>
     </row>
@@ -6240,13 +6237,7 @@
       <c r="A288" t="s">
         <v>306</v>
       </c>
-      <c r="G288">
-        <v>1</v>
-      </c>
-      <c r="H288">
-        <v>1</v>
-      </c>
-      <c r="I288">
+      <c r="Q288">
         <v>1</v>
       </c>
     </row>
@@ -6254,16 +6245,13 @@
       <c r="A289" t="s">
         <v>307</v>
       </c>
-      <c r="D289">
-        <v>1</v>
-      </c>
-      <c r="E289">
-        <v>1</v>
-      </c>
-      <c r="G289">
-        <v>1</v>
-      </c>
-      <c r="H289">
+      <c r="Q289">
+        <v>1</v>
+      </c>
+      <c r="R289">
+        <v>1</v>
+      </c>
+      <c r="T289">
         <v>1</v>
       </c>
     </row>
@@ -6271,9 +6259,6 @@
       <c r="A290" t="s">
         <v>308</v>
       </c>
-      <c r="E290">
-        <v>1</v>
-      </c>
       <c r="G290">
         <v>1</v>
       </c>
@@ -6281,9 +6266,6 @@
         <v>1</v>
       </c>
       <c r="I290">
-        <v>1</v>
-      </c>
-      <c r="R290">
         <v>1</v>
       </c>
     </row>
@@ -6291,13 +6273,13 @@
       <c r="A291" t="s">
         <v>309</v>
       </c>
-      <c r="D291">
-        <v>1</v>
-      </c>
-      <c r="E291">
-        <v>1</v>
-      </c>
-      <c r="F291">
+      <c r="R291">
+        <v>1</v>
+      </c>
+      <c r="S291">
+        <v>1</v>
+      </c>
+      <c r="T291">
         <v>1</v>
       </c>
     </row>
@@ -6305,13 +6287,13 @@
       <c r="A292" t="s">
         <v>310</v>
       </c>
-      <c r="B292">
-        <v>1</v>
-      </c>
-      <c r="D292">
-        <v>1</v>
-      </c>
-      <c r="G292">
+      <c r="C292">
+        <v>1</v>
+      </c>
+      <c r="O292">
+        <v>1</v>
+      </c>
+      <c r="R292">
         <v>1</v>
       </c>
     </row>
@@ -6319,22 +6301,19 @@
       <c r="A293" t="s">
         <v>311</v>
       </c>
-      <c r="B293">
-        <v>1</v>
-      </c>
       <c r="C293">
         <v>1</v>
       </c>
-      <c r="D293">
-        <v>1</v>
-      </c>
-      <c r="G293">
-        <v>1</v>
-      </c>
-      <c r="H293">
-        <v>1</v>
-      </c>
       <c r="O293">
+        <v>1</v>
+      </c>
+      <c r="Q293">
+        <v>1</v>
+      </c>
+      <c r="R293">
+        <v>1</v>
+      </c>
+      <c r="T293">
         <v>1</v>
       </c>
     </row>
@@ -6342,16 +6321,13 @@
       <c r="A294" t="s">
         <v>312</v>
       </c>
-      <c r="D294">
-        <v>1</v>
-      </c>
-      <c r="E294">
+      <c r="O294">
+        <v>1</v>
+      </c>
+      <c r="Q294">
         <v>1</v>
       </c>
       <c r="R294">
-        <v>1</v>
-      </c>
-      <c r="S294">
         <v>1</v>
       </c>
     </row>
@@ -6359,19 +6335,16 @@
       <c r="A295" t="s">
         <v>313</v>
       </c>
+      <c r="B295">
+        <v>1</v>
+      </c>
       <c r="D295">
         <v>1</v>
       </c>
-      <c r="G295">
-        <v>1</v>
-      </c>
-      <c r="H295">
-        <v>1</v>
-      </c>
-      <c r="I295">
-        <v>1</v>
-      </c>
-      <c r="S295">
+      <c r="E295">
+        <v>1</v>
+      </c>
+      <c r="R295">
         <v>1</v>
       </c>
     </row>
@@ -6379,19 +6352,13 @@
       <c r="A296" t="s">
         <v>314</v>
       </c>
-      <c r="E296">
-        <v>1</v>
-      </c>
-      <c r="F296">
-        <v>1</v>
-      </c>
-      <c r="H296">
-        <v>1</v>
-      </c>
-      <c r="I296">
+      <c r="R296">
         <v>1</v>
       </c>
       <c r="S296">
+        <v>1</v>
+      </c>
+      <c r="T296">
         <v>1</v>
       </c>
     </row>
@@ -6399,19 +6366,13 @@
       <c r="A297" t="s">
         <v>315</v>
       </c>
-      <c r="K297">
-        <v>1</v>
-      </c>
-      <c r="L297">
-        <v>1</v>
-      </c>
-      <c r="M297">
-        <v>1</v>
-      </c>
-      <c r="P297">
+      <c r="R297">
         <v>1</v>
       </c>
       <c r="S297">
+        <v>1</v>
+      </c>
+      <c r="T297">
         <v>1</v>
       </c>
     </row>
@@ -6419,22 +6380,22 @@
       <c r="A298" t="s">
         <v>316</v>
       </c>
+      <c r="B298">
+        <v>1</v>
+      </c>
+      <c r="C298">
+        <v>1</v>
+      </c>
       <c r="D298">
         <v>1</v>
       </c>
-      <c r="E298">
-        <v>1</v>
-      </c>
       <c r="G298">
         <v>1</v>
       </c>
-      <c r="H298">
-        <v>1</v>
-      </c>
       <c r="K298">
         <v>1</v>
       </c>
-      <c r="S298">
+      <c r="R298">
         <v>1</v>
       </c>
     </row>
@@ -6442,10 +6403,10 @@
       <c r="A299" t="s">
         <v>317</v>
       </c>
-      <c r="E299">
-        <v>1</v>
-      </c>
-      <c r="F299">
+      <c r="B299">
+        <v>1</v>
+      </c>
+      <c r="D299">
         <v>1</v>
       </c>
       <c r="G299">
@@ -6454,10 +6415,16 @@
       <c r="H299">
         <v>1</v>
       </c>
+      <c r="K299">
+        <v>1</v>
+      </c>
       <c r="R299">
         <v>1</v>
       </c>
       <c r="S299">
+        <v>1</v>
+      </c>
+      <c r="T299">
         <v>1</v>
       </c>
     </row>
@@ -6465,13 +6432,10 @@
       <c r="A300" t="s">
         <v>318</v>
       </c>
-      <c r="D300">
-        <v>1</v>
-      </c>
-      <c r="E300">
-        <v>1</v>
-      </c>
-      <c r="G300">
+      <c r="K300">
+        <v>1</v>
+      </c>
+      <c r="L300">
         <v>1</v>
       </c>
       <c r="R300">
@@ -6482,7 +6446,25 @@
       <c r="A301" t="s">
         <v>319</v>
       </c>
-      <c r="J301">
+      <c r="D301">
+        <v>1</v>
+      </c>
+      <c r="G301">
+        <v>1</v>
+      </c>
+      <c r="H301">
+        <v>1</v>
+      </c>
+      <c r="I301">
+        <v>1</v>
+      </c>
+      <c r="K301">
+        <v>1</v>
+      </c>
+      <c r="L301">
+        <v>1</v>
+      </c>
+      <c r="R301">
         <v>1</v>
       </c>
       <c r="S301">
@@ -6496,13 +6478,13 @@
       <c r="A302" t="s">
         <v>320</v>
       </c>
-      <c r="G302">
-        <v>1</v>
-      </c>
-      <c r="H302">
-        <v>1</v>
-      </c>
-      <c r="I302">
+      <c r="D302">
+        <v>1</v>
+      </c>
+      <c r="E302">
+        <v>1</v>
+      </c>
+      <c r="F302">
         <v>1</v>
       </c>
     </row>
@@ -7539,7 +7521,7 @@
     </row>
     <row r="361" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A361" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B361">
         <v>1</v>
@@ -7661,131 +7643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="363" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A363" t="s">
-        <v>380</v>
-      </c>
-      <c r="B363">
-        <v>1</v>
-      </c>
-      <c r="C363">
-        <v>1</v>
-      </c>
-      <c r="D363">
-        <v>1</v>
-      </c>
-      <c r="E363">
-        <v>1</v>
-      </c>
-      <c r="F363">
-        <v>1</v>
-      </c>
-      <c r="G363">
-        <v>1</v>
-      </c>
-      <c r="H363">
-        <v>1</v>
-      </c>
-      <c r="I363">
-        <v>1</v>
-      </c>
-      <c r="J363">
-        <v>1</v>
-      </c>
-      <c r="K363">
-        <v>1</v>
-      </c>
-      <c r="L363">
-        <v>1</v>
-      </c>
-      <c r="M363">
-        <v>1</v>
-      </c>
-      <c r="N363">
-        <v>1</v>
-      </c>
-      <c r="O363">
-        <v>1</v>
-      </c>
-      <c r="P363">
-        <v>1</v>
-      </c>
-      <c r="Q363">
-        <v>1</v>
-      </c>
-      <c r="R363">
-        <v>1</v>
-      </c>
-      <c r="S363">
-        <v>1</v>
-      </c>
-      <c r="T363">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="364" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A364" t="s">
-        <v>381</v>
-      </c>
-      <c r="B364">
-        <v>1</v>
-      </c>
-      <c r="C364">
-        <v>1</v>
-      </c>
-      <c r="D364">
-        <v>1</v>
-      </c>
-      <c r="E364">
-        <v>1</v>
-      </c>
-      <c r="F364">
-        <v>1</v>
-      </c>
-      <c r="G364">
-        <v>1</v>
-      </c>
-      <c r="H364">
-        <v>1</v>
-      </c>
-      <c r="I364">
-        <v>1</v>
-      </c>
-      <c r="J364">
-        <v>1</v>
-      </c>
-      <c r="K364">
-        <v>1</v>
-      </c>
-      <c r="L364">
-        <v>1</v>
-      </c>
-      <c r="M364">
-        <v>1</v>
-      </c>
-      <c r="N364">
-        <v>1</v>
-      </c>
-      <c r="O364">
-        <v>1</v>
-      </c>
-      <c r="P364">
-        <v>1</v>
-      </c>
-      <c r="Q364">
-        <v>1</v>
-      </c>
-      <c r="R364">
-        <v>1</v>
-      </c>
-      <c r="S364">
-        <v>1</v>
-      </c>
-      <c r="T364">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>